--- a/Q-Rahmen_Uebersicht_V1.xlsx
+++ b/Q-Rahmen_Uebersicht_V1.xlsx
@@ -39,7 +39,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="DD.MM.YYYY"/>
+  </numFmts>
   <fonts count="20">
     <font>
       <name val="Calibri"/>
@@ -281,7 +283,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -397,6 +399,15 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -854,23 +865,23 @@
         </is>
       </c>
       <c r="C17" s="9">
-        <f>COUNTIF('1_Q1_Rechtsordnung'!$I$6:$I$97,"belegt")+COUNTIF('1_Q1_Rechtsordnung'!$I$6:$I$97,"gilt")</f>
+        <f>COUNTIF('1_Q1_Rechtsordnung'!$I$6:$I$95,"belegt")+COUNTIF('1_Q1_Rechtsordnung'!$I$6:$I$95,"gilt")</f>
         <v/>
       </c>
       <c r="D17" s="9">
-        <f>COUNTIF('1_Q1_Rechtsordnung'!$I$6:$I$97,"belegt – Betroffenheit offen")</f>
+        <f>COUNTIF('1_Q1_Rechtsordnung'!$I$6:$I$95,"belegt – Betroffenheit offen")</f>
         <v/>
       </c>
       <c r="E17" s="9">
-        <f>COUNTIF('1_Q1_Rechtsordnung'!$I$6:$I$97,"keine Regelung (geprüft)")</f>
+        <f>COUNTIF('1_Q1_Rechtsordnung'!$I$6:$I$95,"keine Regelung (geprüft)")</f>
         <v/>
       </c>
       <c r="F17" s="9">
-        <f>COUNTIF('1_Q1_Rechtsordnung'!$I$6:$I$97,"nicht belegt (Recherche offen)")</f>
+        <f>COUNTIF('1_Q1_Rechtsordnung'!$I$6:$I$95,"nicht belegt (Recherche offen)")</f>
         <v/>
       </c>
       <c r="G17" s="9">
-        <f>COUNTIF('1_Q1_Rechtsordnung'!$I$6:$I$97,"Datenanfrage (nicht öffentlich)")</f>
+        <f>COUNTIF('1_Q1_Rechtsordnung'!$I$6:$I$95,"Datenanfrage (nicht öffentlich)")</f>
         <v/>
       </c>
       <c r="H17" s="9">
@@ -890,23 +901,23 @@
         </is>
       </c>
       <c r="C18" s="9">
-        <f>COUNTIF('1_Q1_Rechtsordnung'!$J$6:$J$97,"belegt")+COUNTIF('1_Q1_Rechtsordnung'!$J$6:$J$97,"gilt")</f>
+        <f>COUNTIF('1_Q1_Rechtsordnung'!$J$6:$J$95,"belegt")+COUNTIF('1_Q1_Rechtsordnung'!$J$6:$J$95,"gilt")</f>
         <v/>
       </c>
       <c r="D18" s="9">
-        <f>COUNTIF('1_Q1_Rechtsordnung'!$J$6:$J$97,"belegt – Betroffenheit offen")</f>
+        <f>COUNTIF('1_Q1_Rechtsordnung'!$J$6:$J$95,"belegt – Betroffenheit offen")</f>
         <v/>
       </c>
       <c r="E18" s="9">
-        <f>COUNTIF('1_Q1_Rechtsordnung'!$J$6:$J$97,"keine Regelung (geprüft)")</f>
+        <f>COUNTIF('1_Q1_Rechtsordnung'!$J$6:$J$95,"keine Regelung (geprüft)")</f>
         <v/>
       </c>
       <c r="F18" s="9">
-        <f>COUNTIF('1_Q1_Rechtsordnung'!$J$6:$J$97,"nicht belegt (Recherche offen)")</f>
+        <f>COUNTIF('1_Q1_Rechtsordnung'!$J$6:$J$95,"nicht belegt (Recherche offen)")</f>
         <v/>
       </c>
       <c r="G18" s="9">
-        <f>COUNTIF('1_Q1_Rechtsordnung'!$J$6:$J$97,"Datenanfrage (nicht öffentlich)")</f>
+        <f>COUNTIF('1_Q1_Rechtsordnung'!$J$6:$J$95,"Datenanfrage (nicht öffentlich)")</f>
         <v/>
       </c>
       <c r="H18" s="9">
@@ -926,23 +937,23 @@
         </is>
       </c>
       <c r="C19" s="9">
-        <f>COUNTIF('1_Q1_Rechtsordnung'!$K$6:$K$97,"belegt")+COUNTIF('1_Q1_Rechtsordnung'!$K$6:$K$97,"gilt")</f>
+        <f>COUNTIF('1_Q1_Rechtsordnung'!$K$6:$K$95,"belegt")+COUNTIF('1_Q1_Rechtsordnung'!$K$6:$K$95,"gilt")</f>
         <v/>
       </c>
       <c r="D19" s="9">
-        <f>COUNTIF('1_Q1_Rechtsordnung'!$K$6:$K$97,"belegt – Betroffenheit offen")</f>
+        <f>COUNTIF('1_Q1_Rechtsordnung'!$K$6:$K$95,"belegt – Betroffenheit offen")</f>
         <v/>
       </c>
       <c r="E19" s="9">
-        <f>COUNTIF('1_Q1_Rechtsordnung'!$K$6:$K$97,"keine Regelung (geprüft)")</f>
+        <f>COUNTIF('1_Q1_Rechtsordnung'!$K$6:$K$95,"keine Regelung (geprüft)")</f>
         <v/>
       </c>
       <c r="F19" s="9">
-        <f>COUNTIF('1_Q1_Rechtsordnung'!$K$6:$K$97,"nicht belegt (Recherche offen)")</f>
+        <f>COUNTIF('1_Q1_Rechtsordnung'!$K$6:$K$95,"nicht belegt (Recherche offen)")</f>
         <v/>
       </c>
       <c r="G19" s="9">
-        <f>COUNTIF('1_Q1_Rechtsordnung'!$K$6:$K$97,"Datenanfrage (nicht öffentlich)")</f>
+        <f>COUNTIF('1_Q1_Rechtsordnung'!$K$6:$K$95,"Datenanfrage (nicht öffentlich)")</f>
         <v/>
       </c>
       <c r="H19" s="9">
@@ -1078,23 +1089,23 @@
         </is>
       </c>
       <c r="C23" s="9">
-        <f>COUNTIF('3_Q3_Klima_Energie'!$I$6:$I$33,"belegt")+COUNTIF('3_Q3_Klima_Energie'!$I$6:$I$33,"gilt")</f>
+        <f>COUNTIF('3_Q3_Klima_Energie'!$I$6:$I$32,"belegt")+COUNTIF('3_Q3_Klima_Energie'!$I$6:$I$32,"gilt")</f>
         <v/>
       </c>
       <c r="D23" s="9">
-        <f>COUNTIF('3_Q3_Klima_Energie'!$I$6:$I$33,"belegt – Betroffenheit offen")</f>
+        <f>COUNTIF('3_Q3_Klima_Energie'!$I$6:$I$32,"belegt – Betroffenheit offen")</f>
         <v/>
       </c>
       <c r="E23" s="9">
-        <f>COUNTIF('3_Q3_Klima_Energie'!$I$6:$I$33,"keine Regelung (geprüft)")</f>
+        <f>COUNTIF('3_Q3_Klima_Energie'!$I$6:$I$32,"keine Regelung (geprüft)")</f>
         <v/>
       </c>
       <c r="F23" s="9">
-        <f>COUNTIF('3_Q3_Klima_Energie'!$I$6:$I$33,"nicht belegt (Recherche offen)")</f>
+        <f>COUNTIF('3_Q3_Klima_Energie'!$I$6:$I$32,"nicht belegt (Recherche offen)")</f>
         <v/>
       </c>
       <c r="G23" s="9">
-        <f>COUNTIF('3_Q3_Klima_Energie'!$I$6:$I$33,"Datenanfrage (nicht öffentlich)")</f>
+        <f>COUNTIF('3_Q3_Klima_Energie'!$I$6:$I$32,"Datenanfrage (nicht öffentlich)")</f>
         <v/>
       </c>
       <c r="H23" s="9">
@@ -1114,23 +1125,23 @@
         </is>
       </c>
       <c r="C24" s="9">
-        <f>COUNTIF('3_Q3_Klima_Energie'!$J$6:$J$33,"belegt")+COUNTIF('3_Q3_Klima_Energie'!$J$6:$J$33,"gilt")</f>
+        <f>COUNTIF('3_Q3_Klima_Energie'!$J$6:$J$32,"belegt")+COUNTIF('3_Q3_Klima_Energie'!$J$6:$J$32,"gilt")</f>
         <v/>
       </c>
       <c r="D24" s="9">
-        <f>COUNTIF('3_Q3_Klima_Energie'!$J$6:$J$33,"belegt – Betroffenheit offen")</f>
+        <f>COUNTIF('3_Q3_Klima_Energie'!$J$6:$J$32,"belegt – Betroffenheit offen")</f>
         <v/>
       </c>
       <c r="E24" s="9">
-        <f>COUNTIF('3_Q3_Klima_Energie'!$J$6:$J$33,"keine Regelung (geprüft)")</f>
+        <f>COUNTIF('3_Q3_Klima_Energie'!$J$6:$J$32,"keine Regelung (geprüft)")</f>
         <v/>
       </c>
       <c r="F24" s="9">
-        <f>COUNTIF('3_Q3_Klima_Energie'!$J$6:$J$33,"nicht belegt (Recherche offen)")</f>
+        <f>COUNTIF('3_Q3_Klima_Energie'!$J$6:$J$32,"nicht belegt (Recherche offen)")</f>
         <v/>
       </c>
       <c r="G24" s="9">
-        <f>COUNTIF('3_Q3_Klima_Energie'!$J$6:$J$33,"Datenanfrage (nicht öffentlich)")</f>
+        <f>COUNTIF('3_Q3_Klima_Energie'!$J$6:$J$32,"Datenanfrage (nicht öffentlich)")</f>
         <v/>
       </c>
       <c r="H24" s="9">
@@ -1150,23 +1161,23 @@
         </is>
       </c>
       <c r="C25" s="9">
-        <f>COUNTIF('3_Q3_Klima_Energie'!$K$6:$K$33,"belegt")+COUNTIF('3_Q3_Klima_Energie'!$K$6:$K$33,"gilt")</f>
+        <f>COUNTIF('3_Q3_Klima_Energie'!$K$6:$K$32,"belegt")+COUNTIF('3_Q3_Klima_Energie'!$K$6:$K$32,"gilt")</f>
         <v/>
       </c>
       <c r="D25" s="9">
-        <f>COUNTIF('3_Q3_Klima_Energie'!$K$6:$K$33,"belegt – Betroffenheit offen")</f>
+        <f>COUNTIF('3_Q3_Klima_Energie'!$K$6:$K$32,"belegt – Betroffenheit offen")</f>
         <v/>
       </c>
       <c r="E25" s="9">
-        <f>COUNTIF('3_Q3_Klima_Energie'!$K$6:$K$33,"keine Regelung (geprüft)")</f>
+        <f>COUNTIF('3_Q3_Klima_Energie'!$K$6:$K$32,"keine Regelung (geprüft)")</f>
         <v/>
       </c>
       <c r="F25" s="9">
-        <f>COUNTIF('3_Q3_Klima_Energie'!$K$6:$K$33,"nicht belegt (Recherche offen)")</f>
+        <f>COUNTIF('3_Q3_Klima_Energie'!$K$6:$K$32,"nicht belegt (Recherche offen)")</f>
         <v/>
       </c>
       <c r="G25" s="9">
-        <f>COUNTIF('3_Q3_Klima_Energie'!$K$6:$K$33,"Datenanfrage (nicht öffentlich)")</f>
+        <f>COUNTIF('3_Q3_Klima_Energie'!$K$6:$K$32,"Datenanfrage (nicht öffentlich)")</f>
         <v/>
       </c>
       <c r="H25" s="9">
@@ -1414,23 +1425,23 @@
         </is>
       </c>
       <c r="C32" s="9">
-        <f>COUNTIF('6_Q6_Bestellung'!$I$6:$I$37,"belegt")+COUNTIF('6_Q6_Bestellung'!$I$6:$I$37,"gilt")</f>
+        <f>COUNTIF('6_Q6_Bestellung'!$I$6:$I$36,"belegt")+COUNTIF('6_Q6_Bestellung'!$I$6:$I$36,"gilt")</f>
         <v/>
       </c>
       <c r="D32" s="9">
-        <f>COUNTIF('6_Q6_Bestellung'!$I$6:$I$37,"belegt – Betroffenheit offen")</f>
+        <f>COUNTIF('6_Q6_Bestellung'!$I$6:$I$36,"belegt – Betroffenheit offen")</f>
         <v/>
       </c>
       <c r="E32" s="9">
-        <f>COUNTIF('6_Q6_Bestellung'!$I$6:$I$37,"keine Regelung (geprüft)")</f>
+        <f>COUNTIF('6_Q6_Bestellung'!$I$6:$I$36,"keine Regelung (geprüft)")</f>
         <v/>
       </c>
       <c r="F32" s="9">
-        <f>COUNTIF('6_Q6_Bestellung'!$I$6:$I$37,"nicht belegt (Recherche offen)")</f>
+        <f>COUNTIF('6_Q6_Bestellung'!$I$6:$I$36,"nicht belegt (Recherche offen)")</f>
         <v/>
       </c>
       <c r="G32" s="9">
-        <f>COUNTIF('6_Q6_Bestellung'!$I$6:$I$37,"Datenanfrage (nicht öffentlich)")</f>
+        <f>COUNTIF('6_Q6_Bestellung'!$I$6:$I$36,"Datenanfrage (nicht öffentlich)")</f>
         <v/>
       </c>
       <c r="H32" s="9">
@@ -1450,23 +1461,23 @@
         </is>
       </c>
       <c r="C33" s="9">
-        <f>COUNTIF('6_Q6_Bestellung'!$J$6:$J$37,"belegt")+COUNTIF('6_Q6_Bestellung'!$J$6:$J$37,"gilt")</f>
+        <f>COUNTIF('6_Q6_Bestellung'!$J$6:$J$36,"belegt")+COUNTIF('6_Q6_Bestellung'!$J$6:$J$36,"gilt")</f>
         <v/>
       </c>
       <c r="D33" s="9">
-        <f>COUNTIF('6_Q6_Bestellung'!$J$6:$J$37,"belegt – Betroffenheit offen")</f>
+        <f>COUNTIF('6_Q6_Bestellung'!$J$6:$J$36,"belegt – Betroffenheit offen")</f>
         <v/>
       </c>
       <c r="E33" s="9">
-        <f>COUNTIF('6_Q6_Bestellung'!$J$6:$J$37,"keine Regelung (geprüft)")</f>
+        <f>COUNTIF('6_Q6_Bestellung'!$J$6:$J$36,"keine Regelung (geprüft)")</f>
         <v/>
       </c>
       <c r="F33" s="9">
-        <f>COUNTIF('6_Q6_Bestellung'!$J$6:$J$37,"nicht belegt (Recherche offen)")</f>
+        <f>COUNTIF('6_Q6_Bestellung'!$J$6:$J$36,"nicht belegt (Recherche offen)")</f>
         <v/>
       </c>
       <c r="G33" s="9">
-        <f>COUNTIF('6_Q6_Bestellung'!$J$6:$J$37,"Datenanfrage (nicht öffentlich)")</f>
+        <f>COUNTIF('6_Q6_Bestellung'!$J$6:$J$36,"Datenanfrage (nicht öffentlich)")</f>
         <v/>
       </c>
       <c r="H33" s="9">
@@ -1486,23 +1497,23 @@
         </is>
       </c>
       <c r="C34" s="9">
-        <f>COUNTIF('6_Q6_Bestellung'!$K$6:$K$37,"belegt")+COUNTIF('6_Q6_Bestellung'!$K$6:$K$37,"gilt")</f>
+        <f>COUNTIF('6_Q6_Bestellung'!$K$6:$K$36,"belegt")+COUNTIF('6_Q6_Bestellung'!$K$6:$K$36,"gilt")</f>
         <v/>
       </c>
       <c r="D34" s="9">
-        <f>COUNTIF('6_Q6_Bestellung'!$K$6:$K$37,"belegt – Betroffenheit offen")</f>
+        <f>COUNTIF('6_Q6_Bestellung'!$K$6:$K$36,"belegt – Betroffenheit offen")</f>
         <v/>
       </c>
       <c r="E34" s="9">
-        <f>COUNTIF('6_Q6_Bestellung'!$K$6:$K$37,"keine Regelung (geprüft)")</f>
+        <f>COUNTIF('6_Q6_Bestellung'!$K$6:$K$36,"keine Regelung (geprüft)")</f>
         <v/>
       </c>
       <c r="F34" s="9">
-        <f>COUNTIF('6_Q6_Bestellung'!$K$6:$K$37,"nicht belegt (Recherche offen)")</f>
+        <f>COUNTIF('6_Q6_Bestellung'!$K$6:$K$36,"nicht belegt (Recherche offen)")</f>
         <v/>
       </c>
       <c r="G34" s="9">
-        <f>COUNTIF('6_Q6_Bestellung'!$K$6:$K$37,"Datenanfrage (nicht öffentlich)")</f>
+        <f>COUNTIF('6_Q6_Bestellung'!$K$6:$K$36,"Datenanfrage (nicht öffentlich)")</f>
         <v/>
       </c>
       <c r="H34" s="9">
@@ -1615,7 +1626,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Link-Status = Herkunft · Test: «getestet OK» = Seite abgerufen; «Quelle bestätigt» = Link stammt von einer Behördenseite; «ungetestet» = in der Sandbox nicht abrufbar (kein defekter Link festgestellt). Herkunft: Kataster · Suchtreffer · Muster (Link nach bekanntem Muster) · Einstiegsseite (Dokument-URL nicht ermittelt).</t>
+          <t>Link-Status: «geprüft · OK» = Link abgerufen und mit Bezeichnung/Referenz abgeglichen (Linkprüfung GitHub-Runner bzw. manuell); «geprüft · korrigiert» = falscher Link ersetzt; «geprüft · manuell prüfen» / «Hinweis» / «nur Einstiegsseite» = noch offen. Herkunft und Confidence stehen in der Spalte «Herkunft · Confidence».</t>
         </is>
       </c>
     </row>
@@ -1741,9 +1752,9 @@
           <t>SR 702.1</t>
         </is>
       </c>
-      <c r="F5" s="49" t="inlineStr">
-        <is>
-          <t>geprüft · korrigiert</t>
+      <c r="F5" s="52" t="inlineStr">
+        <is>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1789,9 +1800,9 @@
           <t>SR 451.11</t>
         </is>
       </c>
-      <c r="F6" s="49" t="inlineStr">
-        <is>
-          <t>geprüft · korrigiert</t>
+      <c r="F6" s="52" t="inlineStr">
+        <is>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1837,9 +1848,9 @@
           <t>SR 451.12</t>
         </is>
       </c>
-      <c r="F7" s="49" t="inlineStr">
-        <is>
-          <t>geprüft · korrigiert</t>
+      <c r="F7" s="52" t="inlineStr">
+        <is>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1885,9 +1896,9 @@
           <t>SR 451.13</t>
         </is>
       </c>
-      <c r="F8" s="49" t="inlineStr">
-        <is>
-          <t>geprüft · korrigiert</t>
+      <c r="F8" s="52" t="inlineStr">
+        <is>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1933,9 +1944,9 @@
           <t>SR 451.31</t>
         </is>
       </c>
-      <c r="F9" s="49" t="inlineStr">
-        <is>
-          <t>geprüft · korrigiert</t>
+      <c r="F9" s="52" t="inlineStr">
+        <is>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1981,9 +1992,9 @@
           <t>SR 451.32</t>
         </is>
       </c>
-      <c r="F10" s="49" t="inlineStr">
-        <is>
-          <t>geprüft · korrigiert</t>
+      <c r="F10" s="52" t="inlineStr">
+        <is>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -2029,9 +2040,9 @@
           <t>SR 451.33</t>
         </is>
       </c>
-      <c r="F11" s="49" t="inlineStr">
-        <is>
-          <t>geprüft · korrigiert</t>
+      <c r="F11" s="52" t="inlineStr">
+        <is>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -2077,9 +2088,9 @@
           <t>SR 451.34</t>
         </is>
       </c>
-      <c r="F12" s="49" t="inlineStr">
-        <is>
-          <t>geprüft · korrigiert</t>
+      <c r="F12" s="52" t="inlineStr">
+        <is>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -2125,9 +2136,9 @@
           <t>SR 451.35</t>
         </is>
       </c>
-      <c r="F13" s="49" t="inlineStr">
-        <is>
-          <t>geprüft · korrigiert</t>
+      <c r="F13" s="52" t="inlineStr">
+        <is>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2173,9 +2184,9 @@
           <t>SR 451.36</t>
         </is>
       </c>
-      <c r="F14" s="49" t="inlineStr">
-        <is>
-          <t>geprüft · korrigiert</t>
+      <c r="F14" s="52" t="inlineStr">
+        <is>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2221,9 +2232,9 @@
           <t>SR 451.37</t>
         </is>
       </c>
-      <c r="F15" s="49" t="inlineStr">
-        <is>
-          <t>geprüft · korrigiert</t>
+      <c r="F15" s="52" t="inlineStr">
+        <is>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2269,9 +2280,9 @@
           <t>SR 921.01</t>
         </is>
       </c>
-      <c r="F16" s="49" t="inlineStr">
-        <is>
-          <t>geprüft · korrigiert</t>
+      <c r="F16" s="52" t="inlineStr">
+        <is>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2317,9 +2328,9 @@
           <t>SR 923.0</t>
         </is>
       </c>
-      <c r="F17" s="49" t="inlineStr">
-        <is>
-          <t>geprüft · korrigiert</t>
+      <c r="F17" s="52" t="inlineStr">
+        <is>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2365,9 +2376,9 @@
           <t>SR 721.100</t>
         </is>
       </c>
-      <c r="F18" s="49" t="inlineStr">
-        <is>
-          <t>geprüft · korrigiert</t>
+      <c r="F18" s="52" t="inlineStr">
+        <is>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2413,9 +2424,9 @@
           <t>SR 721.100.1</t>
         </is>
       </c>
-      <c r="F19" s="49" t="inlineStr">
-        <is>
-          <t>geprüft · korrigiert</t>
+      <c r="F19" s="52" t="inlineStr">
+        <is>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2461,9 +2472,9 @@
           <t>SR 814.41</t>
         </is>
       </c>
-      <c r="F20" s="49" t="inlineStr">
-        <is>
-          <t>geprüft · korrigiert</t>
+      <c r="F20" s="52" t="inlineStr">
+        <is>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2509,9 +2520,9 @@
           <t>SR 814.011</t>
         </is>
       </c>
-      <c r="F21" s="49" t="inlineStr">
-        <is>
-          <t>geprüft · korrigiert</t>
+      <c r="F21" s="52" t="inlineStr">
+        <is>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2557,9 +2568,9 @@
           <t>SR 814.680</t>
         </is>
       </c>
-      <c r="F22" s="49" t="inlineStr">
-        <is>
-          <t>geprüft · korrigiert</t>
+      <c r="F22" s="52" t="inlineStr">
+        <is>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2605,9 +2616,9 @@
           <t>SR 814.600</t>
         </is>
       </c>
-      <c r="F23" s="49" t="inlineStr">
-        <is>
-          <t>geprüft · korrigiert</t>
+      <c r="F23" s="52" t="inlineStr">
+        <is>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2653,9 +2664,9 @@
           <t>SGS 780</t>
         </is>
       </c>
-      <c r="F24" s="49" t="inlineStr">
-        <is>
-          <t>geprüft · korrigiert</t>
+      <c r="F24" s="52" t="inlineStr">
+        <is>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2701,9 +2712,9 @@
           <t>sGS 731.1</t>
         </is>
       </c>
-      <c r="F25" s="49" t="inlineStr">
-        <is>
-          <t>geprüft · korrigiert</t>
+      <c r="F25" s="52" t="inlineStr">
+        <is>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2749,9 +2760,9 @@
           <t>sGS-Nr. verifizieren</t>
         </is>
       </c>
-      <c r="F26" s="49" t="inlineStr">
-        <is>
-          <t>geprüft · korrigiert</t>
+      <c r="F26" s="52" t="inlineStr">
+        <is>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2797,9 +2808,9 @@
           <t>sGS 271.51</t>
         </is>
       </c>
-      <c r="F27" s="49" t="inlineStr">
-        <is>
-          <t>geprüft · korrigiert</t>
+      <c r="F27" s="52" t="inlineStr">
+        <is>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2845,9 +2856,9 @@
           <t>RB-Nr. verifizieren</t>
         </is>
       </c>
-      <c r="F28" s="49" t="inlineStr">
-        <is>
-          <t>geprüft · korrigiert</t>
+      <c r="F28" s="52" t="inlineStr">
+        <is>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2893,9 +2904,9 @@
           <t>RB-Nr. verifizieren</t>
         </is>
       </c>
-      <c r="F29" s="49" t="inlineStr">
-        <is>
-          <t>geprüft · korrigiert</t>
+      <c r="F29" s="52" t="inlineStr">
+        <is>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2941,9 +2952,9 @@
           <t>IVöB: RB 3.3111</t>
         </is>
       </c>
-      <c r="F30" s="49" t="inlineStr">
-        <is>
-          <t>geprüft · korrigiert</t>
+      <c r="F30" s="52" t="inlineStr">
+        <is>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2989,9 +3000,9 @@
           <t>RB 3.3115</t>
         </is>
       </c>
-      <c r="F31" s="49" t="inlineStr">
-        <is>
-          <t>geprüft · korrigiert</t>
+      <c r="F31" s="52" t="inlineStr">
+        <is>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -3039,7 +3050,7 @@
       </c>
       <c r="F32" s="52" t="inlineStr">
         <is>
-          <t>manuell geprüft · OK</t>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -9711,7 +9722,7 @@
       </c>
       <c r="F171" s="52" t="inlineStr">
         <is>
-          <t>manuell geprüft · OK</t>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -9759,7 +9770,7 @@
       </c>
       <c r="F172" s="52" t="inlineStr">
         <is>
-          <t>manuell geprüft · OK</t>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -9775,6 +9786,11 @@
           <t>https://oereblex.bl.ch/api/attachments/22718</t>
         </is>
       </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>https://geo.ur.ch/?Lat=46.9735&amp;Layers=Nutzungsplanung%2CLiegenschaften%2CBaulanddatenbank&amp;Lng=8.5868&amp;Opacity=0%2C0.4%2C1&amp;Visibility=1%2C1%2C1&amp;Zoom=14</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -9802,7 +9818,7 @@
       </c>
       <c r="F173" s="52" t="inlineStr">
         <is>
-          <t>manuell geprüft · OK</t>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -9845,7 +9861,7 @@
       </c>
       <c r="F174" s="52" t="inlineStr">
         <is>
-          <t>manuell geprüft · OK</t>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -9888,7 +9904,7 @@
       </c>
       <c r="F175" s="52" t="inlineStr">
         <is>
-          <t>manuell geprüft · OK</t>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -10316,9 +10332,9 @@
           <t>–</t>
         </is>
       </c>
-      <c r="F185" s="51" t="inlineStr">
-        <is>
-          <t>geprüft · Hinweis</t>
+      <c r="F185" s="52" t="inlineStr">
+        <is>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -10447,7 +10463,7 @@
       </c>
       <c r="F188" s="52" t="inlineStr">
         <is>
-          <t>manuell geprüft · OK</t>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -10495,7 +10511,7 @@
       </c>
       <c r="F189" s="52" t="inlineStr">
         <is>
-          <t>manuell geprüft · OK</t>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -10541,9 +10557,9 @@
           <t>–</t>
         </is>
       </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>geprüft · nur Einstiegsseite</t>
+      <c r="F190" s="52" t="inlineStr">
+        <is>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -10591,7 +10607,7 @@
       </c>
       <c r="F191" s="52" t="inlineStr">
         <is>
-          <t>manuell geprüft · OK</t>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -10744,6 +10760,11 @@
       <c r="I194" t="inlineStr">
         <is>
           <t>https://www.are.admin.ch</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>https://www.seelisberg.ch/files/pdf/Gemeindeordnung.pdf</t>
         </is>
       </c>
     </row>
@@ -16089,7 +16110,7 @@
       </c>
       <c r="F7" s="23" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>konsolidierte Fassung (Fedlex)</t>
         </is>
       </c>
       <c r="G7" s="23" t="inlineStr">
@@ -16129,7 +16150,7 @@
       </c>
       <c r="N7" s="42" t="inlineStr">
         <is>
-          <t>Muster · geprüft · OK</t>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O7" s="23" t="inlineStr">
@@ -16207,7 +16228,7 @@
       </c>
       <c r="N8" s="42" t="inlineStr">
         <is>
-          <t>Kataster · geprüft · OK</t>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O8" s="23" t="inlineStr">
@@ -16215,11 +16236,7 @@
           <t>Katalog · hoch</t>
         </is>
       </c>
-      <c r="P8" s="23" t="inlineStr">
-        <is>
-          <t>Stände im Katalog uneinheitlich → auf aktuellen Fedlex-Stand vereinheitlichen | Stand lt. Katalog uneinheitlich (M/W: 01.07.2026; S: 01.01.1980 (Erstinkrafttreten)) → massgebend ist die konsolidierte Fassung im Fedlex-Link</t>
-        </is>
-      </c>
+      <c r="P8" s="23" t="n"/>
     </row>
     <row r="9" outlineLevel="1" ht="22.35" customHeight="1">
       <c r="A9" s="23" t="inlineStr">
@@ -16289,7 +16306,7 @@
       </c>
       <c r="N9" s="42" t="inlineStr">
         <is>
-          <t>Kataster · geprüft · OK</t>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O9" s="23" t="inlineStr">
@@ -16297,11 +16314,7 @@
           <t>Katalog · hoch</t>
         </is>
       </c>
-      <c r="P9" s="23" t="inlineStr">
-        <is>
-          <t>Stand lt. Katalog uneinheitlich (M/W: 01.07.2026; S: 01.09.2000) → massgebend ist die konsolidierte Fassung im Fedlex-Link</t>
-        </is>
-      </c>
+      <c r="P9" s="23" t="n"/>
     </row>
     <row r="10" outlineLevel="1" ht="32.85" customHeight="1">
       <c r="A10" s="23" t="inlineStr">
@@ -16371,7 +16384,7 @@
       </c>
       <c r="N10" s="42" t="inlineStr">
         <is>
-          <t>Suchtreffer · geprüft · OK</t>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O10" s="23" t="inlineStr">
@@ -16413,7 +16426,7 @@
       </c>
       <c r="F11" s="23" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>konsolidierte Fassung (Fedlex)</t>
         </is>
       </c>
       <c r="G11" s="23" t="inlineStr">
@@ -16446,14 +16459,14 @@
           <t>Vollzug ZWG; Anhang: Gemeinden mit vermutetem Zweitwohnungsanteil &gt;20 %</t>
         </is>
       </c>
-      <c r="M11" s="43" t="inlineStr">
+      <c r="M11" s="56" t="inlineStr">
         <is>
           <t>https://www.fedlex.admin.ch/eli/cc/2015/887/de</t>
         </is>
       </c>
-      <c r="N11" s="44" t="inlineStr">
-        <is>
-          <t>geprüft · korrigiert</t>
+      <c r="N11" s="42" t="inlineStr">
+        <is>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O11" s="23" t="inlineStr">
@@ -16463,7 +16476,7 @@
       </c>
       <c r="P11" s="23" t="inlineStr">
         <is>
-          <t>Anhang: Seelisberg (UR, BFS-Nr. 1215) aufgeführt; Wil in der SG-Liste nicht aufgeführt; Münchenstein: BL-Teil der Liste nicht eingesehen | Linkprüfung 14.10.2026: Link zeigte nur auf die Einstiegsseite https://www.are.admin.ch; richtig: SR 702.1 «Zweitwohnungsverordnung vom 4. Dezember 2015 (ZWV)». Alter Link: https://www.are.admin.ch</t>
+          <t>Anhang: Seelisberg (UR, BFS-Nr. 1215) aufgeführt; Wil in der SG-Liste nicht aufgeführt; Münchenstein: BL-Teil der Liste nicht eingesehen</t>
         </is>
       </c>
     </row>
@@ -16535,7 +16548,7 @@
       </c>
       <c r="N12" s="42" t="inlineStr">
         <is>
-          <t>Kataster · geprüft · OK</t>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O12" s="23" t="inlineStr">
@@ -16543,11 +16556,7 @@
           <t>Katalog · hoch</t>
         </is>
       </c>
-      <c r="P12" s="23" t="inlineStr">
-        <is>
-          <t>Stand lt. Katalog uneinheitlich (M/W: 01.08.2025; S: 01.01.1967) → massgebend ist die konsolidierte Fassung im Fedlex-Link</t>
-        </is>
-      </c>
+      <c r="P12" s="23" t="n"/>
     </row>
     <row r="13" outlineLevel="1" ht="22.35" customHeight="1">
       <c r="A13" s="23" t="inlineStr">
@@ -16577,7 +16586,7 @@
       </c>
       <c r="F13" s="23" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>konsolidierte Fassung (Fedlex)</t>
         </is>
       </c>
       <c r="G13" s="23" t="inlineStr">
@@ -16617,7 +16626,7 @@
       </c>
       <c r="N13" s="42" t="inlineStr">
         <is>
-          <t>Muster · geprüft · OK</t>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O13" s="23" t="inlineStr">
@@ -16625,11 +16634,7 @@
           <t>Ergänzung · hoch</t>
         </is>
       </c>
-      <c r="P13" s="23" t="inlineStr">
-        <is>
-          <t>Klick-Test ausstehend</t>
-        </is>
-      </c>
+      <c r="P13" s="23" t="n"/>
     </row>
     <row r="14" outlineLevel="1" ht="22.35" customHeight="1">
       <c r="A14" s="23" t="inlineStr">
@@ -16659,7 +16664,7 @@
       </c>
       <c r="F14" s="23" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>konsolidierte Fassung (Fedlex)</t>
         </is>
       </c>
       <c r="G14" s="23" t="inlineStr">
@@ -16692,14 +16697,14 @@
           <t>Rechtsgrundlage BLN</t>
         </is>
       </c>
-      <c r="M14" s="43" t="inlineStr">
+      <c r="M14" s="56" t="inlineStr">
         <is>
           <t>https://www.fedlex.admin.ch/eli/cc/2017/290/de</t>
         </is>
       </c>
-      <c r="N14" s="44" t="inlineStr">
-        <is>
-          <t>geprüft · korrigiert</t>
+      <c r="N14" s="42" t="inlineStr">
+        <is>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O14" s="23" t="inlineStr">
@@ -16707,11 +16712,7 @@
           <t>Ergänzung · hoch</t>
         </is>
       </c>
-      <c r="P14" s="23" t="inlineStr">
-        <is>
-          <t>Linkprüfung 14.10.2026: Link zeigte nur auf die Einstiegsseite https://www.bafu.admin.ch; richtig: SR 451.11 «Verordnung vom 29. März 2017 über das Bundesinventar der Landschaften und Naturdenkmäler (VBLN) ». Alter Link: https://www.bafu.admin.ch</t>
-        </is>
-      </c>
+      <c r="P14" s="23" t="n"/>
     </row>
     <row r="15" outlineLevel="1" ht="22.35" customHeight="1">
       <c r="A15" s="23" t="inlineStr">
@@ -16741,7 +16742,7 @@
       </c>
       <c r="F15" s="23" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>konsolidierte Fassung (Fedlex)</t>
         </is>
       </c>
       <c r="G15" s="23" t="inlineStr">
@@ -16774,14 +16775,14 @@
           <t>Rechtsgrundlage ISOS</t>
         </is>
       </c>
-      <c r="M15" s="43" t="inlineStr">
+      <c r="M15" s="56" t="inlineStr">
         <is>
           <t>https://www.fedlex.admin.ch/eli/cc/2019/673/de</t>
         </is>
       </c>
-      <c r="N15" s="44" t="inlineStr">
-        <is>
-          <t>geprüft · korrigiert</t>
+      <c r="N15" s="42" t="inlineStr">
+        <is>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O15" s="23" t="inlineStr">
@@ -16789,11 +16790,7 @@
           <t>Ergänzung · hoch</t>
         </is>
       </c>
-      <c r="P15" s="23" t="inlineStr">
-        <is>
-          <t>Linkprüfung 14.10.2026: Link zeigte nur auf die Einstiegsseite https://www.bak.admin.ch; richtig: SR 451.12 «Verordnung vom 13. November 2019 über das Bundesinventar der schützenswerten Ortsbilder der Schweiz (VISOS)». Alter Link: https://www.bak.admin.ch</t>
-        </is>
-      </c>
+      <c r="P15" s="23" t="n"/>
     </row>
     <row r="16" outlineLevel="1" ht="22.35" customHeight="1">
       <c r="A16" s="23" t="inlineStr">
@@ -16823,7 +16820,7 @@
       </c>
       <c r="F16" s="23" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>konsolidierte Fassung (Fedlex)</t>
         </is>
       </c>
       <c r="G16" s="23" t="inlineStr">
@@ -16856,14 +16853,14 @@
           <t>Rechtsgrundlage IVS</t>
         </is>
       </c>
-      <c r="M16" s="43" t="inlineStr">
+      <c r="M16" s="56" t="inlineStr">
         <is>
           <t>https://www.fedlex.admin.ch/eli/cc/2010/227/de</t>
         </is>
       </c>
-      <c r="N16" s="44" t="inlineStr">
-        <is>
-          <t>geprüft · korrigiert</t>
+      <c r="N16" s="42" t="inlineStr">
+        <is>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O16" s="23" t="inlineStr">
@@ -16871,11 +16868,7 @@
           <t>Ergänzung · hoch</t>
         </is>
       </c>
-      <c r="P16" s="23" t="inlineStr">
-        <is>
-          <t>Linkprüfung 14.10.2026: Link zeigte nur auf die Einstiegsseite https://www.astra.admin.ch; richtig: SR 451.13 «Verordnung vom 14. April 2010 über das Bundesinventar der historischen Verkehrswege der Schweiz (VIVS) ». Alter Link: https://www.astra.admin.ch</t>
-        </is>
-      </c>
+      <c r="P16" s="23" t="n"/>
     </row>
     <row r="17" outlineLevel="1" ht="32.85" customHeight="1">
       <c r="A17" s="23" t="inlineStr">
@@ -16938,14 +16931,14 @@
           <t>Rechtsgrundlage Bundesinventar: Auengebiete</t>
         </is>
       </c>
-      <c r="M17" s="43" t="inlineStr">
+      <c r="M17" s="56" t="inlineStr">
         <is>
           <t>https://www.fedlex.admin.ch/eli/cc/1992/2080_2080_2080/de</t>
         </is>
       </c>
-      <c r="N17" s="44" t="inlineStr">
-        <is>
-          <t>geprüft · korrigiert</t>
+      <c r="N17" s="42" t="inlineStr">
+        <is>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O17" s="23" t="inlineStr">
@@ -16953,11 +16946,7 @@
           <t>Ergänzung · hoch</t>
         </is>
       </c>
-      <c r="P17" s="23" t="inlineStr">
-        <is>
-          <t>Ergänzung auf Vorgabe des Teams; Fedlex-ELI nicht ermittelt | Linkprüfung 14.10.2026: Link zeigte nur auf die Einstiegsseite https://www.bafu.admin.ch; richtig: SR 451.31 «Verordnung vom 28. Oktober 1992 über den Schutz der Auengebiete von nationaler Bedeutung (Auenverordnung) ». Alter Link: https://www.bafu.admin.ch</t>
-        </is>
-      </c>
+      <c r="P17" s="23" t="n"/>
     </row>
     <row r="18" outlineLevel="1" ht="32.85" customHeight="1">
       <c r="A18" s="23" t="inlineStr">
@@ -17020,14 +17009,14 @@
           <t>Rechtsgrundlage Bundesinventar: Hoch- und Übergangsmoore</t>
         </is>
       </c>
-      <c r="M18" s="43" t="inlineStr">
+      <c r="M18" s="56" t="inlineStr">
         <is>
           <t>https://www.fedlex.admin.ch/eli/cc/1991/270_270_270/de</t>
         </is>
       </c>
-      <c r="N18" s="44" t="inlineStr">
-        <is>
-          <t>geprüft · korrigiert</t>
+      <c r="N18" s="42" t="inlineStr">
+        <is>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O18" s="23" t="inlineStr">
@@ -17035,11 +17024,7 @@
           <t>Ergänzung · hoch</t>
         </is>
       </c>
-      <c r="P18" s="23" t="inlineStr">
-        <is>
-          <t>Ergänzung auf Vorgabe des Teams; Fedlex-ELI nicht ermittelt | Linkprüfung 14.10.2026: Link zeigte nur auf die Einstiegsseite https://www.bafu.admin.ch; richtig: SR 451.32 «Verordnung vom 21. Januar 1991 über den Schutz der Hoch- und Übergangsmoore von nationaler Bedeutung (Hochmoorverordnung) ». Alter Link: https://www.bafu.admin.ch</t>
-        </is>
-      </c>
+      <c r="P18" s="23" t="n"/>
     </row>
     <row r="19" outlineLevel="1" ht="32.85" customHeight="1">
       <c r="A19" s="23" t="inlineStr">
@@ -17102,14 +17087,14 @@
           <t>Rechtsgrundlage Bundesinventar: Flachmoore</t>
         </is>
       </c>
-      <c r="M19" s="43" t="inlineStr">
+      <c r="M19" s="56" t="inlineStr">
         <is>
           <t>https://www.fedlex.admin.ch/eli/cc/1994/2092_2092_2092/de</t>
         </is>
       </c>
-      <c r="N19" s="44" t="inlineStr">
-        <is>
-          <t>geprüft · korrigiert</t>
+      <c r="N19" s="42" t="inlineStr">
+        <is>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O19" s="23" t="inlineStr">
@@ -17117,11 +17102,7 @@
           <t>Ergänzung · hoch</t>
         </is>
       </c>
-      <c r="P19" s="23" t="inlineStr">
-        <is>
-          <t>Ergänzung auf Vorgabe des Teams; Fedlex-ELI nicht ermittelt | Linkprüfung 14.10.2026: Link zeigte nur auf die Einstiegsseite https://www.bafu.admin.ch; richtig: SR 451.33 «Verordnung vom 7. September 1994 über den Schutz der Flachmoore von nationaler Bedeutung (Flachmoorverordnung) ». Alter Link: https://www.bafu.admin.ch</t>
-        </is>
-      </c>
+      <c r="P19" s="23" t="n"/>
     </row>
     <row r="20" outlineLevel="1" ht="32.85" customHeight="1">
       <c r="A20" s="23" t="inlineStr">
@@ -17184,14 +17165,14 @@
           <t>Rechtsgrundlage Bundesinventar: Amphibienlaichgebiete</t>
         </is>
       </c>
-      <c r="M20" s="43" t="inlineStr">
+      <c r="M20" s="56" t="inlineStr">
         <is>
           <t>https://www.fedlex.admin.ch/eli/cc/2001/328/de</t>
         </is>
       </c>
-      <c r="N20" s="44" t="inlineStr">
-        <is>
-          <t>geprüft · korrigiert</t>
+      <c r="N20" s="42" t="inlineStr">
+        <is>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O20" s="23" t="inlineStr">
@@ -17199,11 +17180,7 @@
           <t>Ergänzung · hoch</t>
         </is>
       </c>
-      <c r="P20" s="23" t="inlineStr">
-        <is>
-          <t>Ergänzung auf Vorgabe des Teams; Fedlex-ELI nicht ermittelt | Linkprüfung 14.10.2026: Link zeigte nur auf die Einstiegsseite https://www.bafu.admin.ch; richtig: SR 451.34 «Verordnung vom 15. Juni 2001 über den Schutz der Amphibienlaichgebiete von nationaler Bedeutung (Amphibienlaichgebiete-Verordnung; AlgV) ». Alter Link: https://www.bafu.admin.ch</t>
-        </is>
-      </c>
+      <c r="P20" s="23" t="n"/>
     </row>
     <row r="21" outlineLevel="1" ht="32.85" customHeight="1">
       <c r="A21" s="23" t="inlineStr">
@@ -17266,14 +17243,14 @@
           <t>Rechtsgrundlage Bundesinventar: Moorlandschaften</t>
         </is>
       </c>
-      <c r="M21" s="43" t="inlineStr">
+      <c r="M21" s="56" t="inlineStr">
         <is>
           <t>https://www.fedlex.admin.ch/eli/cc/1996/1839_1839_1839/de</t>
         </is>
       </c>
-      <c r="N21" s="44" t="inlineStr">
-        <is>
-          <t>geprüft · korrigiert</t>
+      <c r="N21" s="42" t="inlineStr">
+        <is>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O21" s="23" t="inlineStr">
@@ -17281,11 +17258,7 @@
           <t>Ergänzung · hoch</t>
         </is>
       </c>
-      <c r="P21" s="23" t="inlineStr">
-        <is>
-          <t>Ergänzung auf Vorgabe des Teams; Fedlex-ELI nicht ermittelt | Linkprüfung 14.10.2026: Link zeigte nur auf die Einstiegsseite https://www.bafu.admin.ch; richtig: SR 451.35 «Verordnung vom 1. Mai 1996 über den Schutz der Moorlandschaften von besonderer Schönheit und von nationaler Bedeutung (Moorlandschaftsverordnung) ». Alter Link: https://www.bafu.admin.ch</t>
-        </is>
-      </c>
+      <c r="P21" s="23" t="n"/>
     </row>
     <row r="22" outlineLevel="1" ht="32.85" customHeight="1">
       <c r="A22" s="23" t="inlineStr">
@@ -17348,14 +17321,14 @@
           <t>Rechtsgrundlage Bundesinventar: Pärke von nationaler Bedeutung</t>
         </is>
       </c>
-      <c r="M22" s="43" t="inlineStr">
+      <c r="M22" s="56" t="inlineStr">
         <is>
           <t>https://www.fedlex.admin.ch/eli/cc/2007/743/de</t>
         </is>
       </c>
-      <c r="N22" s="44" t="inlineStr">
-        <is>
-          <t>geprüft · korrigiert</t>
+      <c r="N22" s="42" t="inlineStr">
+        <is>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O22" s="23" t="inlineStr">
@@ -17363,11 +17336,7 @@
           <t>Ergänzung · hoch</t>
         </is>
       </c>
-      <c r="P22" s="23" t="inlineStr">
-        <is>
-          <t>Ergänzung auf Vorgabe des Teams; Fedlex-ELI nicht ermittelt | Linkprüfung 14.10.2026: Link zeigte nur auf die Einstiegsseite https://www.bafu.admin.ch; richtig: SR 451.36 «Verordnung vom 7. November 2007 über die Pärke von nationaler Bedeutung (Pärkeverordnung, PäV)». Alter Link: https://www.bafu.admin.ch</t>
-        </is>
-      </c>
+      <c r="P22" s="23" t="n"/>
     </row>
     <row r="23" outlineLevel="1" ht="32.85" customHeight="1">
       <c r="A23" s="23" t="inlineStr">
@@ -17430,14 +17399,14 @@
           <t>Rechtsgrundlage Bundesinventar: Trockenwiesen und -weiden</t>
         </is>
       </c>
-      <c r="M23" s="43" t="inlineStr">
+      <c r="M23" s="56" t="inlineStr">
         <is>
           <t>https://www.fedlex.admin.ch/eli/cc/2010/38/de</t>
         </is>
       </c>
-      <c r="N23" s="44" t="inlineStr">
-        <is>
-          <t>geprüft · korrigiert</t>
+      <c r="N23" s="42" t="inlineStr">
+        <is>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O23" s="23" t="inlineStr">
@@ -17445,11 +17414,7 @@
           <t>Ergänzung · hoch</t>
         </is>
       </c>
-      <c r="P23" s="23" t="inlineStr">
-        <is>
-          <t>Ergänzung auf Vorgabe des Teams; Fedlex-ELI nicht ermittelt | Linkprüfung 14.10.2026: Link zeigte nur auf die Einstiegsseite https://www.bafu.admin.ch; richtig: SR 451.37 «Verordnung vom 13. Januar 2010 über den Schutz der Trockenwiesen und -weiden von nationaler Bedeutung (Trockenwiesenverordnung, TwwV) ». Alter Link: https://www.bafu.admin.ch</t>
-        </is>
-      </c>
+      <c r="P23" s="23" t="n"/>
     </row>
     <row r="24" outlineLevel="1" ht="32.85" customHeight="1">
       <c r="A24" s="23" t="inlineStr">
@@ -17519,7 +17484,7 @@
       </c>
       <c r="N24" s="42" t="inlineStr">
         <is>
-          <t>Kataster · geprüft · OK</t>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O24" s="23" t="inlineStr">
@@ -17527,11 +17492,7 @@
           <t>Katalog · hoch</t>
         </is>
       </c>
-      <c r="P24" s="23" t="inlineStr">
-        <is>
-          <t>Stand lt. Katalog uneinheitlich (M/W: 01.08.2025; S: 01.11.1992) → konsolidierte Fassung im Link</t>
-        </is>
-      </c>
+      <c r="P24" s="23" t="n"/>
     </row>
     <row r="25" outlineLevel="1" ht="22.35" customHeight="1">
       <c r="A25" s="23" t="inlineStr">
@@ -17601,7 +17562,7 @@
       </c>
       <c r="N25" s="42" t="inlineStr">
         <is>
-          <t>Muster · geprüft · OK</t>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O25" s="23" t="inlineStr">
@@ -17611,7 +17572,7 @@
       </c>
       <c r="P25" s="23" t="inlineStr">
         <is>
-          <t>Klick-Test ausstehend; Art. 5 = Grundlage GEP</t>
+          <t>Art. 5 GSchV = Grundlage GEP</t>
         </is>
       </c>
     </row>
@@ -17683,7 +17644,7 @@
       </c>
       <c r="N26" s="42" t="inlineStr">
         <is>
-          <t>Kataster · geprüft · OK</t>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O26" s="23" t="inlineStr">
@@ -17691,11 +17652,7 @@
           <t>Katalog · hoch</t>
         </is>
       </c>
-      <c r="P26" s="23" t="inlineStr">
-        <is>
-          <t>Stand lt. Katalog uneinheitlich (M/W: 01.08.2025; S: 01.01.1993) → massgebend ist die konsolidierte Fassung im Fedlex-Link</t>
-        </is>
-      </c>
+      <c r="P26" s="23" t="n"/>
     </row>
     <row r="27" outlineLevel="1" ht="22.35" customHeight="1">
       <c r="A27" s="23" t="inlineStr">
@@ -17758,14 +17715,14 @@
           <t>Vollzug WaG</t>
         </is>
       </c>
-      <c r="M27" s="43" t="inlineStr">
+      <c r="M27" s="56" t="inlineStr">
         <is>
           <t>https://www.fedlex.admin.ch/eli/cc/1992/2538_2538_2538/de</t>
         </is>
       </c>
-      <c r="N27" s="44" t="inlineStr">
-        <is>
-          <t>geprüft · korrigiert</t>
+      <c r="N27" s="42" t="inlineStr">
+        <is>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O27" s="23" t="inlineStr">
@@ -17773,11 +17730,7 @@
           <t>Ergänzung · hoch</t>
         </is>
       </c>
-      <c r="P27" s="23" t="inlineStr">
-        <is>
-          <t>Linkprüfung 14.10.2026: Link zeigte nur auf die Einstiegsseite https://www.bafu.admin.ch; richtig: SR 921.01 «Verordnung vom 30. November 1992 über den Wald (Waldverordnung, WaV)». Alter Link: https://www.bafu.admin.ch</t>
-        </is>
-      </c>
+      <c r="P27" s="23" t="n"/>
     </row>
     <row r="28" outlineLevel="1" ht="22.35" customHeight="1">
       <c r="A28" s="23" t="inlineStr">
@@ -17807,7 +17760,7 @@
       </c>
       <c r="F28" s="23" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>konsolidierte Fassung (Fedlex)</t>
         </is>
       </c>
       <c r="G28" s="23" t="inlineStr">
@@ -17847,7 +17800,7 @@
       </c>
       <c r="N28" s="42" t="inlineStr">
         <is>
-          <t>Muster · geprüft · OK</t>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O28" s="23" t="inlineStr">
@@ -17855,11 +17808,7 @@
           <t>Ergänzung · hoch</t>
         </is>
       </c>
-      <c r="P28" s="23" t="inlineStr">
-        <is>
-          <t>Klick-Test ausstehend</t>
-        </is>
-      </c>
+      <c r="P28" s="23" t="n"/>
     </row>
     <row r="29" outlineLevel="1" ht="22.35" customHeight="1">
       <c r="A29" s="23" t="inlineStr">
@@ -17889,7 +17838,7 @@
       </c>
       <c r="F29" s="23" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>konsolidierte Fassung (Fedlex)</t>
         </is>
       </c>
       <c r="G29" s="23" t="inlineStr">
@@ -17922,14 +17871,14 @@
           <t>Fischereischutz, Lebensräume, Gewässer</t>
         </is>
       </c>
-      <c r="M29" s="43" t="inlineStr">
+      <c r="M29" s="56" t="inlineStr">
         <is>
           <t>https://www.fedlex.admin.ch/eli/cc/1991/2259_2259_2259/de</t>
         </is>
       </c>
-      <c r="N29" s="44" t="inlineStr">
-        <is>
-          <t>geprüft · korrigiert</t>
+      <c r="N29" s="42" t="inlineStr">
+        <is>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O29" s="23" t="inlineStr">
@@ -17937,11 +17886,7 @@
           <t>Ergänzung · hoch</t>
         </is>
       </c>
-      <c r="P29" s="23" t="inlineStr">
-        <is>
-          <t>Linkprüfung 14.10.2026: Link zeigte nur auf die Einstiegsseite https://www.bafu.admin.ch; richtig: SR 923.0 «Bundesgesetz vom 21. Juni 1991 über die Fischerei (BGF)». Alter Link: https://www.bafu.admin.ch</t>
-        </is>
-      </c>
+      <c r="P29" s="23" t="n"/>
     </row>
     <row r="30" outlineLevel="1" ht="22.35" customHeight="1">
       <c r="A30" s="23" t="inlineStr">
@@ -18011,7 +17956,7 @@
       </c>
       <c r="N30" s="42" t="inlineStr">
         <is>
-          <t>Kataster · geprüft · OK</t>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O30" s="23" t="inlineStr">
@@ -18019,11 +17964,7 @@
           <t>Katalog · hoch</t>
         </is>
       </c>
-      <c r="P30" s="23" t="inlineStr">
-        <is>
-          <t>Stand lt. Katalog uneinheitlich (M/W: 01.08.2026; S: 01.01.1985) → massgebend ist die konsolidierte Fassung im Fedlex-Link</t>
-        </is>
-      </c>
+      <c r="P30" s="23" t="n"/>
     </row>
     <row r="31" outlineLevel="1" ht="22.35" customHeight="1">
       <c r="A31" s="23" t="inlineStr">
@@ -18093,7 +18034,7 @@
       </c>
       <c r="N31" s="42" t="inlineStr">
         <is>
-          <t>Kataster · geprüft · OK</t>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O31" s="23" t="inlineStr">
@@ -18101,11 +18042,7 @@
           <t>Katalog · hoch</t>
         </is>
       </c>
-      <c r="P31" s="23" t="inlineStr">
-        <is>
-          <t>Stand lt. Katalog uneinheitlich (M/W: 01.04.2026; S: 01.01.2018) → massgebend ist die konsolidierte Fassung im Fedlex-Link</t>
-        </is>
-      </c>
+      <c r="P31" s="23" t="n"/>
     </row>
     <row r="32" outlineLevel="1" ht="22.35" customHeight="1">
       <c r="A32" s="23" t="inlineStr">
@@ -18175,7 +18112,7 @@
       </c>
       <c r="N32" s="42" t="inlineStr">
         <is>
-          <t>Muster · geprüft · OK</t>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O32" s="23" t="inlineStr">
@@ -18183,11 +18120,7 @@
           <t>Ergänzung · hoch</t>
         </is>
       </c>
-      <c r="P32" s="23" t="inlineStr">
-        <is>
-          <t>Klick-Test ausstehend</t>
-        </is>
-      </c>
+      <c r="P32" s="23" t="n"/>
     </row>
     <row r="33" outlineLevel="1" ht="22.35" customHeight="1">
       <c r="A33" s="23" t="inlineStr">
@@ -18217,7 +18150,7 @@
       </c>
       <c r="F33" s="23" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>konsolidierte Fassung (Fedlex)</t>
         </is>
       </c>
       <c r="G33" s="23" t="inlineStr">
@@ -18257,7 +18190,7 @@
       </c>
       <c r="N33" s="42" t="inlineStr">
         <is>
-          <t>Muster · geprüft · OK</t>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O33" s="23" t="inlineStr">
@@ -18265,11 +18198,7 @@
           <t>Ergänzung · hoch</t>
         </is>
       </c>
-      <c r="P33" s="23" t="inlineStr">
-        <is>
-          <t>Im Katalog nicht geführt; Klick-Test ausstehend</t>
-        </is>
-      </c>
+      <c r="P33" s="23" t="n"/>
     </row>
     <row r="34" outlineLevel="1" ht="22.35" customHeight="1">
       <c r="A34" s="23" t="inlineStr">
@@ -18299,7 +18228,7 @@
       </c>
       <c r="F34" s="23" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>konsolidierte Fassung (Fedlex)</t>
         </is>
       </c>
       <c r="G34" s="23" t="inlineStr">
@@ -18339,7 +18268,7 @@
       </c>
       <c r="N34" s="42" t="inlineStr">
         <is>
-          <t>Muster · geprüft · OK</t>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O34" s="23" t="inlineStr">
@@ -18347,11 +18276,7 @@
           <t>Ergänzung · hoch</t>
         </is>
       </c>
-      <c r="P34" s="23" t="inlineStr">
-        <is>
-          <t>Im Katalog nicht geführt; Klick-Test ausstehend</t>
-        </is>
-      </c>
+      <c r="P34" s="23" t="n"/>
     </row>
     <row r="35" outlineLevel="1" ht="22.35" customHeight="1">
       <c r="A35" s="23" t="inlineStr">
@@ -18421,7 +18346,7 @@
       </c>
       <c r="N35" s="42" t="inlineStr">
         <is>
-          <t>Kataster · geprüft · OK</t>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O35" s="23" t="inlineStr">
@@ -18429,11 +18354,7 @@
           <t>Katalog · hoch</t>
         </is>
       </c>
-      <c r="P35" s="23" t="inlineStr">
-        <is>
-          <t>Stand lt. Katalog uneinheitlich (01.01.2025) → massgebend ist die konsolidierte Fassung im Fedlex-Link</t>
-        </is>
-      </c>
+      <c r="P35" s="23" t="n"/>
     </row>
     <row r="36" outlineLevel="1" ht="22.35" customHeight="1">
       <c r="A36" s="23" t="inlineStr">
@@ -18458,7 +18379,7 @@
       </c>
       <c r="E36" s="23" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>AS 2024 679</t>
         </is>
       </c>
       <c r="F36" s="23" t="inlineStr">
@@ -18503,17 +18424,17 @@
       </c>
       <c r="N36" s="42" t="inlineStr">
         <is>
-          <t>manuell geprüft · OK</t>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O36" s="23" t="inlineStr">
         <is>
-          <t>Ergänzung · mittel</t>
+          <t>Ergänzung · hoch</t>
         </is>
       </c>
       <c r="P36" s="23" t="inlineStr">
         <is>
-          <t>Manuell geprüft 14.10.2026: Link auf Fedlex-Erlass (AS 2024 679) ersetzt und geprüft, OK</t>
+          <t>Änderungserlass (Mantelerlass) ohne eigene SR-Nummer; die Änderungen sind in EnG und StromVG konsolidiert</t>
         </is>
       </c>
     </row>
@@ -18545,7 +18466,7 @@
       </c>
       <c r="F37" s="23" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>konsolidierte Fassung (Fedlex)</t>
         </is>
       </c>
       <c r="G37" s="23" t="inlineStr">
@@ -18578,14 +18499,14 @@
           <t>Hochwasserschutz, Gefahrenkarten, Raumbedarf Gewässer</t>
         </is>
       </c>
-      <c r="M37" s="43" t="inlineStr">
+      <c r="M37" s="56" t="inlineStr">
         <is>
           <t>https://www.fedlex.admin.ch/eli/cc/1993/234_234_234/de</t>
         </is>
       </c>
-      <c r="N37" s="44" t="inlineStr">
-        <is>
-          <t>geprüft · korrigiert</t>
+      <c r="N37" s="42" t="inlineStr">
+        <is>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O37" s="23" t="inlineStr">
@@ -18593,11 +18514,7 @@
           <t>Ergänzung · hoch</t>
         </is>
       </c>
-      <c r="P37" s="23" t="inlineStr">
-        <is>
-          <t>Linkprüfung 14.10.2026: Link zeigte nur auf die Einstiegsseite https://www.bafu.admin.ch; richtig: SR 721.100 «Bundesgesetz vom 21. Juni 1991 über den Wasserbau (Wasserbaugesetz, WBG)». Alter Link: https://www.bafu.admin.ch</t>
-        </is>
-      </c>
+      <c r="P37" s="23" t="n"/>
     </row>
     <row r="38" outlineLevel="1" ht="22.35" customHeight="1">
       <c r="A38" s="23" t="inlineStr">
@@ -18627,7 +18544,7 @@
       </c>
       <c r="F38" s="23" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>konsolidierte Fassung (Fedlex)</t>
         </is>
       </c>
       <c r="G38" s="23" t="inlineStr">
@@ -18660,14 +18577,14 @@
           <t>Vollzug WBG</t>
         </is>
       </c>
-      <c r="M38" s="43" t="inlineStr">
+      <c r="M38" s="56" t="inlineStr">
         <is>
           <t>https://www.fedlex.admin.ch/eli/cc/2025/450/de</t>
         </is>
       </c>
-      <c r="N38" s="44" t="inlineStr">
-        <is>
-          <t>geprüft · korrigiert</t>
+      <c r="N38" s="42" t="inlineStr">
+        <is>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O38" s="23" t="inlineStr">
@@ -18675,11 +18592,7 @@
           <t>Ergänzung · hoch</t>
         </is>
       </c>
-      <c r="P38" s="23" t="inlineStr">
-        <is>
-          <t>Linkprüfung 14.10.2026: Link zeigte nur auf die Einstiegsseite https://www.bafu.admin.ch; richtig: SR 721.100.1 «Verordnung vom 25. Juni 2025 über den Wasserbau (Wasserbauverordnung, WBV)». Alter Link: https://www.bafu.admin.ch</t>
-        </is>
-      </c>
+      <c r="P38" s="23" t="n"/>
     </row>
     <row r="39" outlineLevel="1" ht="32.85" customHeight="1">
       <c r="A39" s="23" t="inlineStr">
@@ -18709,7 +18622,7 @@
       </c>
       <c r="F39" s="23" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>konsolidierte Fassung (Fedlex)</t>
         </is>
       </c>
       <c r="G39" s="23" t="inlineStr">
@@ -18749,7 +18662,7 @@
       </c>
       <c r="N39" s="42" t="inlineStr">
         <is>
-          <t>Suchtreffer · geprüft · OK</t>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O39" s="23" t="inlineStr">
@@ -18787,7 +18700,7 @@
       </c>
       <c r="F40" s="23" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>konsolidierte Fassung (Fedlex)</t>
         </is>
       </c>
       <c r="G40" s="23" t="inlineStr">
@@ -18827,7 +18740,7 @@
       </c>
       <c r="N40" s="42" t="inlineStr">
         <is>
-          <t>Muster · geprüft · OK</t>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O40" s="23" t="inlineStr">
@@ -18869,7 +18782,7 @@
       </c>
       <c r="F41" s="23" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>konsolidierte Fassung (Fedlex)</t>
         </is>
       </c>
       <c r="G41" s="23" t="inlineStr">
@@ -18902,14 +18815,14 @@
           <t>Lärmgrenzwerte, Empfindlichkeitsstufen</t>
         </is>
       </c>
-      <c r="M41" s="43" t="inlineStr">
+      <c r="M41" s="56" t="inlineStr">
         <is>
           <t>https://www.fedlex.admin.ch/eli/cc/1987/338_338_338/de</t>
         </is>
       </c>
-      <c r="N41" s="44" t="inlineStr">
-        <is>
-          <t>geprüft · korrigiert</t>
+      <c r="N41" s="42" t="inlineStr">
+        <is>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O41" s="23" t="inlineStr">
@@ -18917,11 +18830,7 @@
           <t>Ergänzung · hoch</t>
         </is>
       </c>
-      <c r="P41" s="23" t="inlineStr">
-        <is>
-          <t>Im Katalog nicht geführt | Linkprüfung 14.10.2026: Link zeigte auf ELI cc/1987/1_1_1 (SR keine); richtig: SR 814.41 «Lärmschutz-Verordnung vom 15. Dezember 1986 (LSV)». Alter Link: https://www.fedlex.admin.ch/eli/cc/1987/1_1_1/de</t>
-        </is>
-      </c>
+      <c r="P41" s="23" t="n"/>
     </row>
     <row r="42" outlineLevel="1" ht="22.35" customHeight="1">
       <c r="A42" s="23" t="inlineStr">
@@ -18951,7 +18860,7 @@
       </c>
       <c r="F42" s="23" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>konsolidierte Fassung (Fedlex)</t>
         </is>
       </c>
       <c r="G42" s="23" t="inlineStr">
@@ -18991,7 +18900,7 @@
       </c>
       <c r="N42" s="42" t="inlineStr">
         <is>
-          <t>Muster · geprüft · OK</t>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O42" s="23" t="inlineStr">
@@ -18999,11 +18908,7 @@
           <t>Ergänzung · hoch</t>
         </is>
       </c>
-      <c r="P42" s="23" t="inlineStr">
-        <is>
-          <t>Im Katalog nicht geführt</t>
-        </is>
-      </c>
+      <c r="P42" s="23" t="n"/>
     </row>
     <row r="43" outlineLevel="1" ht="22.35" customHeight="1">
       <c r="A43" s="23" t="inlineStr">
@@ -19033,7 +18938,7 @@
       </c>
       <c r="F43" s="23" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>konsolidierte Fassung (Fedlex)</t>
         </is>
       </c>
       <c r="G43" s="23" t="inlineStr">
@@ -19073,7 +18978,7 @@
       </c>
       <c r="N43" s="42" t="inlineStr">
         <is>
-          <t>Muster · geprüft · OK</t>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O43" s="23" t="inlineStr">
@@ -19081,11 +18986,7 @@
           <t>Ergänzung · hoch</t>
         </is>
       </c>
-      <c r="P43" s="23" t="inlineStr">
-        <is>
-          <t>Im Katalog nicht geführt</t>
-        </is>
-      </c>
+      <c r="P43" s="23" t="n"/>
     </row>
     <row r="44" outlineLevel="1" ht="22.35" customHeight="1">
       <c r="A44" s="23" t="inlineStr">
@@ -19115,7 +19016,7 @@
       </c>
       <c r="F44" s="23" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>konsolidierte Fassung (Fedlex)</t>
         </is>
       </c>
       <c r="G44" s="23" t="inlineStr">
@@ -19148,14 +19049,14 @@
           <t>UVP-Pflicht</t>
         </is>
       </c>
-      <c r="M44" s="43" t="inlineStr">
+      <c r="M44" s="56" t="inlineStr">
         <is>
           <t>https://www.fedlex.admin.ch/eli/cc/1988/1931_1931_1931/de</t>
         </is>
       </c>
-      <c r="N44" s="44" t="inlineStr">
-        <is>
-          <t>geprüft · korrigiert</t>
+      <c r="N44" s="42" t="inlineStr">
+        <is>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O44" s="23" t="inlineStr">
@@ -19163,11 +19064,7 @@
           <t>Ergänzung · hoch</t>
         </is>
       </c>
-      <c r="P44" s="23" t="inlineStr">
-        <is>
-          <t>Fedlex-ELI nicht ermittelt → Einstiegsseite BAFU | Linkprüfung 14.10.2026: Link zeigte nur auf die Einstiegsseite https://www.bafu.admin.ch; richtig: SR 814.011 «Verordnung vom 19. Oktober 1988 über die Umweltverträglichkeitsprüfung (UVPV)». Alter Link: https://www.bafu.admin.ch</t>
-        </is>
-      </c>
+      <c r="P44" s="23" t="n"/>
     </row>
     <row r="45" outlineLevel="1" ht="22.35" customHeight="1">
       <c r="A45" s="23" t="inlineStr">
@@ -19197,7 +19094,7 @@
       </c>
       <c r="F45" s="23" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>konsolidierte Fassung (Fedlex)</t>
         </is>
       </c>
       <c r="G45" s="23" t="inlineStr">
@@ -19230,14 +19127,14 @@
           <t>Belastete Standorte, Kataster</t>
         </is>
       </c>
-      <c r="M45" s="43" t="inlineStr">
+      <c r="M45" s="56" t="inlineStr">
         <is>
           <t>https://www.fedlex.admin.ch/eli/cc/1998/2261_2261_2261/de</t>
         </is>
       </c>
-      <c r="N45" s="44" t="inlineStr">
-        <is>
-          <t>geprüft · korrigiert</t>
+      <c r="N45" s="42" t="inlineStr">
+        <is>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O45" s="23" t="inlineStr">
@@ -19245,11 +19142,7 @@
           <t>Ergänzung · hoch</t>
         </is>
       </c>
-      <c r="P45" s="23" t="inlineStr">
-        <is>
-          <t>Fedlex-ELI nicht ermittelt → Einstiegsseite BAFU | Linkprüfung 14.10.2026: Link zeigte nur auf die Einstiegsseite https://www.bafu.admin.ch; richtig: SR 814.680 «Verordnung vom 26. August 1998 über die Sanierung von belasteten Standorten (Altlasten-Verordnung, AltlV)». Alter Link: https://www.bafu.admin.ch</t>
-        </is>
-      </c>
+      <c r="P45" s="23" t="n"/>
     </row>
     <row r="46" outlineLevel="1" ht="22.35" customHeight="1">
       <c r="A46" s="23" t="inlineStr">
@@ -19279,7 +19172,7 @@
       </c>
       <c r="F46" s="23" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>konsolidierte Fassung (Fedlex)</t>
         </is>
       </c>
       <c r="G46" s="23" t="inlineStr">
@@ -19312,14 +19205,14 @@
           <t>Abfall, Kreislauf, Rückbaumaterial</t>
         </is>
       </c>
-      <c r="M46" s="43" t="inlineStr">
+      <c r="M46" s="56" t="inlineStr">
         <is>
           <t>https://www.fedlex.admin.ch/eli/cc/2015/891/de</t>
         </is>
       </c>
-      <c r="N46" s="44" t="inlineStr">
-        <is>
-          <t>geprüft · korrigiert</t>
+      <c r="N46" s="42" t="inlineStr">
+        <is>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O46" s="23" t="inlineStr">
@@ -19327,11 +19220,7 @@
           <t>Ergänzung · hoch</t>
         </is>
       </c>
-      <c r="P46" s="23" t="inlineStr">
-        <is>
-          <t>Fedlex-ELI nicht ermittelt → Einstiegsseite BAFU | Linkprüfung 14.10.2026: Link zeigte nur auf die Einstiegsseite https://www.bafu.admin.ch; richtig: SR 814.600 «Verordnung vom 4. Dezember 2015 über die Vermeidung und die Entsorgung von Abfällen (Abfallverordnung, VVEA)». Alter Link: https://www.bafu.admin.ch</t>
-        </is>
-      </c>
+      <c r="P46" s="23" t="n"/>
     </row>
     <row r="47" ht="19.5" customHeight="1">
       <c r="A47" s="21" t="inlineStr">
@@ -19423,7 +19312,7 @@
       </c>
       <c r="N48" s="42" t="inlineStr">
         <is>
-          <t>Suchtreffer · geprüft · OK</t>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O48" s="23" t="inlineStr">
@@ -19433,7 +19322,7 @@
       </c>
       <c r="P48" s="23" t="inlineStr">
         <is>
-          <t>Katalog-Link zeigt auf die Fassung von 2001 (alte IVöB): https://www.bpuk.ch/fileadmin/Dokumente/bpuk/public/de/konko… – ersetzt. Beitritt SG per 01.06.2023 (sg.ch); UR: Landrat Juni 2022 (ur.ch); BL: Beitritt nicht verifiziert</t>
+          <t>Katalog verwies auf die alte IVöB vom 15.03.2001, ersetzt durch IVöB 2019. Beitritt SG und UR per 01.06.2023; BL: Beitrittsdatum nicht verifiziert</t>
         </is>
       </c>
     </row>
@@ -19527,7 +19416,7 @@
       </c>
       <c r="N50" s="42" t="inlineStr">
         <is>
-          <t>Kataster · geprüft · OK</t>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O50" s="23" t="inlineStr">
@@ -19605,7 +19494,7 @@
       </c>
       <c r="N51" s="42" t="inlineStr">
         <is>
-          <t>Kataster · geprüft · OK</t>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O51" s="23" t="inlineStr">
@@ -19683,7 +19572,7 @@
       </c>
       <c r="N52" s="42" t="inlineStr">
         <is>
-          <t>Kataster · geprüft · OK</t>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O52" s="23" t="inlineStr">
@@ -19761,7 +19650,7 @@
       </c>
       <c r="N53" s="42" t="inlineStr">
         <is>
-          <t>Kataster · geprüft · OK</t>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O53" s="23" t="inlineStr">
@@ -19771,7 +19660,7 @@
       </c>
       <c r="P53" s="23" t="inlineStr">
         <is>
-          <t>Zugehöriges EG IVöB (Gesetz) und Beitrittszeitpunkt BL nicht verifiziert</t>
+          <t>Zugehöriges EG IVöB BL (SGS 420) ist in Mappe 6 erfasst; Beitrittszeitpunkt BL nicht verifiziert</t>
         </is>
       </c>
     </row>
@@ -19843,7 +19732,7 @@
       </c>
       <c r="N54" s="42" t="inlineStr">
         <is>
-          <t>Muster · geprüft · OK</t>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O54" s="23" t="inlineStr">
@@ -19851,11 +19740,7 @@
           <t>Ergänzung · hoch</t>
         </is>
       </c>
-      <c r="P54" s="23" t="inlineStr">
-        <is>
-          <t>Suchtreffer: Gesetzestext bl.clex.ch/data/790/de; aktuelle Fassung beim Klick prüfen</t>
-        </is>
-      </c>
+      <c r="P54" s="23" t="n"/>
     </row>
     <row r="55" outlineLevel="1" ht="22.35" customHeight="1">
       <c r="A55" s="23" t="inlineStr">
@@ -19878,7 +19763,7 @@
           <t>Gesetz über den Denkmal- und Heimatschutz (DHG BL)</t>
         </is>
       </c>
-      <c r="E55" s="45" t="inlineStr">
+      <c r="E55" s="23" t="inlineStr">
         <is>
           <t>SGS 791</t>
         </is>
@@ -19918,26 +19803,22 @@
           <t>Unterschutzstellung, Bauinventar, Ortsbildschutz</t>
         </is>
       </c>
-      <c r="M55" s="43" t="inlineStr">
+      <c r="M55" s="56" t="inlineStr">
         <is>
           <t>https://bl.clex.ch/app/de/texts_of_law/791</t>
         </is>
       </c>
-      <c r="N55" s="44" t="inlineStr">
-        <is>
-          <t>geprüft · korrigiert</t>
+      <c r="N55" s="42" t="inlineStr">
+        <is>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O55" s="23" t="inlineStr">
         <is>
-          <t>Ergänzung · mittel</t>
-        </is>
-      </c>
-      <c r="P55" s="23" t="inlineStr">
-        <is>
-          <t>SGS-Nr. aus Fachwissen; Klick-Test ausstehend | Linkprüfung 14.10.2026: SGS 780 ist das Umweltschutzgesetz BL (USG BL); das DHG BL ist SGS 791 (Titel lt. Sammlung: «Gesetz über den Denkmal- und Heimatschutz (DHG)»). Alter Link: https://bl.clex.ch/app/de/texts_of_law/780 | Referenz alt: SGS 780</t>
-        </is>
-      </c>
+          <t>Ergänzung · hoch</t>
+        </is>
+      </c>
+      <c r="P55" s="23" t="n"/>
     </row>
     <row r="56" outlineLevel="1" ht="22.35" customHeight="1">
       <c r="A56" s="23" t="inlineStr">
@@ -20007,19 +19888,15 @@
       </c>
       <c r="N56" s="42" t="inlineStr">
         <is>
-          <t>Muster · geprüft · OK</t>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O56" s="23" t="inlineStr">
         <is>
-          <t>Ergänzung · mittel</t>
-        </is>
-      </c>
-      <c r="P56" s="23" t="inlineStr">
-        <is>
-          <t>SGS-Nr. aus Fachwissen; Klick-Test ausstehend</t>
-        </is>
-      </c>
+          <t>Ergänzung · hoch</t>
+        </is>
+      </c>
+      <c r="P56" s="23" t="n"/>
     </row>
     <row r="57" ht="19.5" customHeight="1">
       <c r="A57" s="21" t="inlineStr">
@@ -20104,14 +19981,14 @@
           <t>Baubewilligung, Zonenkonformität, Planungsverfahren</t>
         </is>
       </c>
-      <c r="M58" s="43" t="inlineStr">
+      <c r="M58" s="56" t="inlineStr">
         <is>
           <t>https://www.gesetzessammlung.sg.ch/app/de/texts_of_law/731.1</t>
         </is>
       </c>
-      <c r="N58" s="44" t="inlineStr">
-        <is>
-          <t>geprüft · korrigiert</t>
+      <c r="N58" s="42" t="inlineStr">
+        <is>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O58" s="23" t="inlineStr">
@@ -20119,11 +19996,7 @@
           <t>Katalog · hoch</t>
         </is>
       </c>
-      <c r="P58" s="23" t="inlineStr">
-        <is>
-          <t>Linkprüfung 14.10.2026: Link auf Standardform der Sammlung vereinheitlicht (731.1 «Planungs- und Baugesetz (PBG)»). Alter Link: https://www.gesetzessammlung.sg.ch/data/731.1/de</t>
-        </is>
-      </c>
+      <c r="P58" s="23" t="n"/>
     </row>
     <row r="59" outlineLevel="1" ht="22.35" customHeight="1">
       <c r="A59" s="23" t="inlineStr">
@@ -20193,7 +20066,7 @@
       </c>
       <c r="N59" s="42" t="inlineStr">
         <is>
-          <t>Kataster · geprüft · OK</t>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O59" s="23" t="inlineStr">
@@ -20275,7 +20148,7 @@
       </c>
       <c r="N60" s="42" t="inlineStr">
         <is>
-          <t>Kataster · geprüft · OK</t>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O60" s="23" t="inlineStr">
@@ -20303,10 +20176,10 @@
       </c>
       <c r="D61" s="25" t="inlineStr">
         <is>
-          <t>Wasserbaugesetz SG</t>
-        </is>
-      </c>
-      <c r="E61" s="45" t="inlineStr">
+          <t>Wasserbaugesetz SG (WBG)</t>
+        </is>
+      </c>
+      <c r="E61" s="23" t="inlineStr">
         <is>
           <t>sGS 734.1</t>
         </is>
@@ -20331,9 +20204,9 @@
           <t>n. a.</t>
         </is>
       </c>
-      <c r="J61" s="30" t="inlineStr">
-        <is>
-          <t>nicht belegt (Recherche offen)</t>
+      <c r="J61" s="57" t="inlineStr">
+        <is>
+          <t>belegt</t>
         </is>
       </c>
       <c r="K61" s="29" t="inlineStr">
@@ -20346,26 +20219,22 @@
           <t>Hochwasserschutz, Gefahrenkarten, Gewässerraum</t>
         </is>
       </c>
-      <c r="M61" s="43" t="inlineStr">
+      <c r="M61" s="56" t="inlineStr">
         <is>
           <t>https://www.gesetzessammlung.sg.ch/app/de/texts_of_law/734.1</t>
         </is>
       </c>
-      <c r="N61" s="44" t="inlineStr">
-        <is>
-          <t>geprüft · korrigiert</t>
+      <c r="N61" s="42" t="inlineStr">
+        <is>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O61" s="23" t="inlineStr">
         <is>
-          <t>Ergänzung · tief</t>
-        </is>
-      </c>
-      <c r="P61" s="23" t="inlineStr">
-        <is>
-          <t>Linkprüfung 14.10.2026: Link zeigte auf die Startseite sg.ch; Wasserbaugesetz SG = sGS 734.1 (Titel lt. Sammlung: «Wasserbaugesetz (WBG)»). Alter Link: https://www.sg.ch | Referenz alt: sGS-Nr. verifizieren</t>
-        </is>
-      </c>
+          <t>Ergänzung · hoch</t>
+        </is>
+      </c>
+      <c r="P61" s="23" t="n"/>
     </row>
     <row r="62" outlineLevel="1" ht="32.85" customHeight="1">
       <c r="A62" s="23" t="inlineStr">
@@ -20435,7 +20304,7 @@
       </c>
       <c r="N62" s="42" t="inlineStr">
         <is>
-          <t>Suchtreffer · geprüft · OK</t>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O62" s="23" t="inlineStr">
@@ -20513,19 +20382,15 @@
       </c>
       <c r="N63" s="42" t="inlineStr">
         <is>
-          <t>Muster · geprüft · OK</t>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O63" s="23" t="inlineStr">
         <is>
-          <t>Ergänzung · mittel</t>
-        </is>
-      </c>
-      <c r="P63" s="23" t="inlineStr">
-        <is>
-          <t>Nummer und Erlassdatum aus Gemeinde-Schutzverordnungen (oereblex.sg.ch) belegt; aktuelle Fassung beim Klick prüfen</t>
-        </is>
-      </c>
+          <t>Ergänzung · hoch</t>
+        </is>
+      </c>
+      <c r="P63" s="23" t="n"/>
     </row>
     <row r="64" outlineLevel="1" ht="22.35" customHeight="1">
       <c r="A64" s="23" t="inlineStr">
@@ -20545,17 +20410,17 @@
       </c>
       <c r="D64" s="25" t="inlineStr">
         <is>
-          <t>Verordnung betreffend den Schutz von Naturkörpern und Altertümern</t>
-        </is>
-      </c>
-      <c r="E64" s="45" t="inlineStr">
+          <t>Verordnung über die Sicherung und Überlieferung von Naturkörpern</t>
+        </is>
+      </c>
+      <c r="E64" s="23" t="inlineStr">
         <is>
           <t>sGS 271.53</t>
         </is>
       </c>
       <c r="F64" s="23" t="inlineStr">
         <is>
-          <t>Erlass 21.03.1933</t>
+          <t>–</t>
         </is>
       </c>
       <c r="G64" s="23" t="inlineStr">
@@ -20588,24 +20453,24 @@
           <t>Schutz von Altertümern (Archäologie/Denkmal)</t>
         </is>
       </c>
-      <c r="M64" s="43" t="inlineStr">
+      <c r="M64" s="56" t="inlineStr">
         <is>
           <t>https://www.gesetzessammlung.sg.ch/app/de/texts_of_law/271.53</t>
         </is>
       </c>
-      <c r="N64" s="44" t="inlineStr">
-        <is>
-          <t>geprüft · korrigiert</t>
+      <c r="N64" s="42" t="inlineStr">
+        <is>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O64" s="23" t="inlineStr">
         <is>
-          <t>Ergänzung · mittel</t>
+          <t>Ergänzung · hoch</t>
         </is>
       </c>
       <c r="P64" s="23" t="inlineStr">
         <is>
-          <t>Nummer aus Gemeinde-Schutzverordnung belegt; Geltung beim Klick prüfen | Linkprüfung 14.10.2026: sGS 271.51 ist seit 31.07.2019 aufgehoben; ersetzt durch den Nachfolgeerlass sGS 271.53 (Titel lt. Sammlung: «Verordnung über die Sicherung und Überlieferung von Naturkörpern»). Alter Link: https://www.gesetzessammlung.sg.ch/app/de/texts_of_law/271.51 | Referenz alt: sGS 271.51</t>
+          <t>Nachfolgeerlass der aufgehobenen sGS 271.51 «Verordnung betreffend den Schutz von Naturkörpern und Altertümern» (in Vollzug bis 31.07.2019)</t>
         </is>
       </c>
     </row>
@@ -20677,7 +20542,7 @@
       </c>
       <c r="N65" s="42" t="inlineStr">
         <is>
-          <t>Suchtreffer · geprüft · OK</t>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O65" s="23" t="inlineStr">
@@ -20685,11 +20550,7 @@
           <t>Ergänzung · hoch</t>
         </is>
       </c>
-      <c r="P65" s="23" t="inlineStr">
-        <is>
-          <t>Suchtreffer sg.ch</t>
-        </is>
-      </c>
+      <c r="P65" s="23" t="n"/>
     </row>
     <row r="66" outlineLevel="1" ht="32.85" customHeight="1">
       <c r="A66" s="23" t="inlineStr">
@@ -20759,7 +20620,7 @@
       </c>
       <c r="N66" s="42" t="inlineStr">
         <is>
-          <t>Suchtreffer · geprüft · OK</t>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O66" s="23" t="inlineStr">
@@ -20767,11 +20628,7 @@
           <t>Ergänzung · hoch</t>
         </is>
       </c>
-      <c r="P66" s="23" t="inlineStr">
-        <is>
-          <t>Suchtreffer sg.ch (Rechtsgrundlagen-Liste)</t>
-        </is>
-      </c>
+      <c r="P66" s="23" t="n"/>
     </row>
     <row r="67" ht="19.5" customHeight="1">
       <c r="A67" s="21" t="inlineStr">
@@ -20863,7 +20720,7 @@
       </c>
       <c r="N68" s="42" t="inlineStr">
         <is>
-          <t>Kataster · geprüft · OK</t>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O68" s="23" t="inlineStr">
@@ -20941,7 +20798,7 @@
       </c>
       <c r="N69" s="42" t="inlineStr">
         <is>
-          <t>Kataster · geprüft · OK</t>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O69" s="23" t="inlineStr">
@@ -20969,10 +20826,10 @@
       </c>
       <c r="D70" s="25" t="inlineStr">
         <is>
-          <t>Natur- und Heimatschutzrecht Uri (kantonale Erlasse)</t>
-        </is>
-      </c>
-      <c r="E70" s="45" t="inlineStr">
+          <t>Gesetz über den Natur- und Heimatschutz Uri</t>
+        </is>
+      </c>
+      <c r="E70" s="23" t="inlineStr">
         <is>
           <t>RB 10.5101</t>
         </is>
@@ -21002,9 +20859,9 @@
           <t>n. a.</t>
         </is>
       </c>
-      <c r="K70" s="30" t="inlineStr">
-        <is>
-          <t>nicht belegt (Recherche offen)</t>
+      <c r="K70" s="57" t="inlineStr">
+        <is>
+          <t>belegt</t>
         </is>
       </c>
       <c r="L70" s="23" t="inlineStr">
@@ -21012,26 +20869,22 @@
           <t>Kantonale Schutzobjekte, Schutzinventar</t>
         </is>
       </c>
-      <c r="M70" s="43" t="inlineStr">
+      <c r="M70" s="56" t="inlineStr">
         <is>
           <t>https://rechtsbuch.ur.ch/app/de/texts_of_law/10.5101</t>
         </is>
       </c>
-      <c r="N70" s="44" t="inlineStr">
-        <is>
-          <t>geprüft · korrigiert</t>
+      <c r="N70" s="42" t="inlineStr">
+        <is>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O70" s="23" t="inlineStr">
         <is>
-          <t>Ergänzung · tief</t>
-        </is>
-      </c>
-      <c r="P70" s="23" t="inlineStr">
-        <is>
-          <t>Linkprüfung 14.10.2026: Link zeigte auf die Startseite ur.ch; Gesetz über den Natur- und Heimatschutz = RB 10.5101 (Titel lt. Sammlung: «Gesetz über den Natur- und Heimatschutz»). Alter Link: https://www.ur.ch | Referenz alt: RB-Nr. verifizieren</t>
-        </is>
-      </c>
+          <t>Ergänzung · hoch</t>
+        </is>
+      </c>
+      <c r="P70" s="23" t="n"/>
     </row>
     <row r="71" outlineLevel="1" ht="22.35" customHeight="1">
       <c r="A71" s="23" t="inlineStr">
@@ -21051,7 +20904,7 @@
       </c>
       <c r="D71" s="25" t="inlineStr">
         <is>
-          <t>Kantonale Energiegesetzgebung Uri</t>
+          <t>Energiegesetz des Kantons Uri (EnG)</t>
         </is>
       </c>
       <c r="E71" s="23" t="inlineStr">
@@ -21101,7 +20954,7 @@
       </c>
       <c r="N71" s="42" t="inlineStr">
         <is>
-          <t>Kataster · geprüft · OK</t>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O71" s="23" t="inlineStr">
@@ -21111,7 +20964,7 @@
       </c>
       <c r="P71" s="23" t="inlineStr">
         <is>
-          <t>Stand 2000 vermutlich Erstinkrafttreten → aktuelle Fassung/Revisionen prüfen | verlinkte Nummer 40.7211 ist «Energiegesetz des Kantons Uri (EnG)»; Bezeichnung lautet anders</t>
+          <t>Stand im Katalog (01.01.2000) vermutlich Erstinkrafttreten; massgebend ist die aktuelle Fassung im Rechtsbuch</t>
         </is>
       </c>
     </row>
@@ -21133,10 +20986,10 @@
       </c>
       <c r="D72" s="25" t="inlineStr">
         <is>
-          <t>Wasserbau-/Naturgefahrenrecht Uri</t>
-        </is>
-      </c>
-      <c r="E72" s="45" t="inlineStr">
+          <t>Wasserbaugesetz Uri (WBG)</t>
+        </is>
+      </c>
+      <c r="E72" s="23" t="inlineStr">
         <is>
           <t>RB 40.1211</t>
         </is>
@@ -21166,9 +21019,9 @@
           <t>n. a.</t>
         </is>
       </c>
-      <c r="K72" s="30" t="inlineStr">
-        <is>
-          <t>nicht belegt (Recherche offen)</t>
+      <c r="K72" s="57" t="inlineStr">
+        <is>
+          <t>belegt</t>
         </is>
       </c>
       <c r="L72" s="23" t="inlineStr">
@@ -21176,26 +21029,22 @@
           <t>Hochwasser-/Naturgefahrenschutz, Gefahrenkarten</t>
         </is>
       </c>
-      <c r="M72" s="43" t="inlineStr">
+      <c r="M72" s="56" t="inlineStr">
         <is>
           <t>https://rechtsbuch.ur.ch/app/de/texts_of_law/40.1211</t>
         </is>
       </c>
-      <c r="N72" s="44" t="inlineStr">
-        <is>
-          <t>geprüft · korrigiert</t>
+      <c r="N72" s="42" t="inlineStr">
+        <is>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O72" s="23" t="inlineStr">
         <is>
-          <t>Ergänzung · tief</t>
-        </is>
-      </c>
-      <c r="P72" s="23" t="inlineStr">
-        <is>
-          <t>Linkprüfung 14.10.2026: Link zeigte auf die Startseite ur.ch; Wasserbaugesetz Uri (WBG) = RB 40.1211 (Titel lt. Sammlung: «Wasserbaugesetz (WBG)»). Alter Link: https://www.ur.ch | Referenz alt: RB-Nr. verifizieren</t>
-        </is>
-      </c>
+          <t>Ergänzung · hoch</t>
+        </is>
+      </c>
+      <c r="P72" s="23" t="n"/>
     </row>
     <row r="73" outlineLevel="1" ht="22.35" customHeight="1">
       <c r="A73" s="23" t="inlineStr">
@@ -21220,7 +21069,7 @@
       </c>
       <c r="E73" s="23" t="inlineStr">
         <is>
-          <t>IVöB: RB 3.3111</t>
+          <t>RB 3.3111</t>
         </is>
       </c>
       <c r="F73" s="23" t="inlineStr">
@@ -21258,14 +21107,14 @@
           <t>IVöB 2019 gilt in Uri; frühere Submissionsverordnung aufgehoben</t>
         </is>
       </c>
-      <c r="M73" s="43" t="inlineStr">
+      <c r="M73" s="56" t="inlineStr">
         <is>
           <t>https://rechtsbuch.ur.ch/app/de/texts_of_law/3.3111</t>
         </is>
       </c>
-      <c r="N73" s="44" t="inlineStr">
-        <is>
-          <t>geprüft · korrigiert</t>
+      <c r="N73" s="42" t="inlineStr">
+        <is>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O73" s="23" t="inlineStr">
@@ -21275,7 +21124,7 @@
       </c>
       <c r="P73" s="23" t="inlineStr">
         <is>
-          <t>Beleg: Schulungsunterlage Baudirektion UR vom 08.05.2023 (Link getestet). Submissionsverordnung RB 3.3112 aufgehoben | Linkprüfung 14.10.2026: Link zeigte auf https://www.ur.ch/_doc/337571 (HTTP 200, «Microsoft PowerPoint - 20230508_Schulung_IVöB_Uri final(2).p»); richtig: RB 3.3111 «Interkantonale Vereinbarung über das öffentliche Beschaffungswesen (IVöB)». Alter Link: https://www.ur.ch/_doc/337571</t>
+          <t>IVöB im Rechtsbuch Uri (RB 3.3111); Inkrafttreten für Uri 01.06.2023; Submissionsverordnung RB 3.3112 aufgehoben</t>
         </is>
       </c>
     </row>
@@ -21292,7 +21141,7 @@
       </c>
       <c r="C74" s="23" t="inlineStr">
         <is>
-          <t>Beschluss</t>
+          <t>Reglement</t>
         </is>
       </c>
       <c r="D74" s="25" t="inlineStr">
@@ -21340,14 +21189,14 @@
           <t>IVöB 2019 gilt in Uri; frühere Submissionsverordnung aufgehoben</t>
         </is>
       </c>
-      <c r="M74" s="43" t="inlineStr">
+      <c r="M74" s="56" t="inlineStr">
         <is>
           <t>https://rechtsbuch.ur.ch/app/de/texts_of_law/3.3115</t>
         </is>
       </c>
-      <c r="N74" s="44" t="inlineStr">
-        <is>
-          <t>geprüft · korrigiert</t>
+      <c r="N74" s="42" t="inlineStr">
+        <is>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O74" s="23" t="inlineStr">
@@ -21355,11 +21204,7 @@
           <t>Ergänzung · hoch</t>
         </is>
       </c>
-      <c r="P74" s="23" t="inlineStr">
-        <is>
-          <t>Beleg: Schulungsunterlage Baudirektion UR vom 08.05.2023 (Link getestet); eigener Reglementstext-Link nicht ermittelt | Linkprüfung 14.10.2026: Link zeigte auf https://www.ur.ch/_doc/337571 (HTTP 200, «Microsoft PowerPoint - 20230508_Schulung_IVöB_Uri final(2).p»); richtig: RB 3.3115 «Reglement über den Vollzug der Interkantonalen Vereinbarung über das öffentliche Beschaffungswesen (Submissionsreglement)». Alter Link: https://www.ur.ch/_doc/337571</t>
-        </is>
-      </c>
+      <c r="P74" s="23" t="n"/>
     </row>
     <row r="75" outlineLevel="1" ht="19.5" customHeight="1">
       <c r="A75" s="21" t="inlineStr">
@@ -21451,7 +21296,7 @@
       </c>
       <c r="N76" s="42" t="inlineStr">
         <is>
-          <t>Kataster · geprüft · OK</t>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O76" s="23" t="inlineStr">
@@ -21459,7 +21304,11 @@
           <t>Katalog · hoch</t>
         </is>
       </c>
-      <c r="P76" s="23" t="n"/>
+      <c r="P76" s="23" t="inlineStr">
+        <is>
+          <t>Mehrfach gelistet, weil das Dokument mehrere Q-Dimensionen abdeckt (Q1, Q2, Q3, Q5)</t>
+        </is>
+      </c>
     </row>
     <row r="77" outlineLevel="1" ht="22.35" customHeight="1">
       <c r="A77" s="23" t="inlineStr">
@@ -21529,7 +21378,7 @@
       </c>
       <c r="N77" s="42" t="inlineStr">
         <is>
-          <t>manuell geprüft · OK</t>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O77" s="23" t="inlineStr">
@@ -21539,7 +21388,7 @@
       </c>
       <c r="P77" s="23" t="inlineStr">
         <is>
-          <t>Manuell geprüft 14.10.2026: Link (oereblex 22718) = Zonenvorschriften Siedlung, OK. Mehrfach gelistet, weil das Dokument mehrere Q-Dimensionen abdeckt (bisherige Bezeichnung: «Kommunale Natur- und Landschaftsschutzfestlegungen»)</t>
+          <t>Mehrfach gelistet, weil das Dokument mehrere Q-Dimensionen abdeckt; Q2-Aspekt: Natur- und Landschaftsschutzfestlegungen</t>
         </is>
       </c>
     </row>
@@ -21611,7 +21460,7 @@
       </c>
       <c r="N78" s="42" t="inlineStr">
         <is>
-          <t>manuell geprüft · OK</t>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O78" s="23" t="inlineStr">
@@ -21621,7 +21470,7 @@
       </c>
       <c r="P78" s="23" t="inlineStr">
         <is>
-          <t>Manuell geprüft 14.10.2026: Link (oereblex 22718) = Zonenvorschriften Siedlung, OK. Mehrfach gelistet, weil das Dokument mehrere Q-Dimensionen abdeckt (bisherige Bezeichnung: «Kommunale Energieplanung / Wärmeversorgung»)</t>
+          <t>Mehrfach gelistet, weil das Dokument mehrere Q-Dimensionen abdeckt; Q3-Aspekt: Energieplanung / Wärmeversorgung</t>
         </is>
       </c>
     </row>
@@ -21693,7 +21542,7 @@
       </c>
       <c r="N79" s="42" t="inlineStr">
         <is>
-          <t>Kataster · geprüft · OK</t>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O79" s="23" t="inlineStr">
@@ -21771,7 +21620,7 @@
       </c>
       <c r="N80" s="42" t="inlineStr">
         <is>
-          <t>manuell geprüft · OK</t>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O80" s="23" t="inlineStr">
@@ -21781,7 +21630,7 @@
       </c>
       <c r="P80" s="23" t="inlineStr">
         <is>
-          <t>Manuell geprüft 14.10.2026: Link (oereblex 22718) = Zonenvorschriften Siedlung, OK. Mehrfach gelistet, weil das Dokument mehrere Q-Dimensionen abdeckt (bisherige Bezeichnung: «Kommunale Schutzverordnung / Ortsbildvorgaben»)</t>
+          <t>Mehrfach gelistet, weil das Dokument mehrere Q-Dimensionen abdeckt; Q5-Aspekt: Schutzverordnung / Ortsbildvorgaben</t>
         </is>
       </c>
     </row>
@@ -21826,9 +21675,9 @@
           <t>öffentlich</t>
         </is>
       </c>
-      <c r="I81" s="30" t="inlineStr">
-        <is>
-          <t>nicht belegt (Recherche offen)</t>
+      <c r="I81" s="57" t="inlineStr">
+        <is>
+          <t>belegt</t>
         </is>
       </c>
       <c r="J81" s="29" t="inlineStr">
@@ -21853,17 +21702,17 @@
       </c>
       <c r="N81" s="42" t="inlineStr">
         <is>
-          <t>manuell geprüft · OK</t>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O81" s="23" t="inlineStr">
         <is>
-          <t>Ergänzung · tief</t>
+          <t>Ergänzung · hoch</t>
         </is>
       </c>
       <c r="P81" s="23" t="inlineStr">
         <is>
-          <t>Manuell geprüft 14.10.2026: Link auf Gemeindeordnung ergänzt</t>
+          <t>Verlinkt ist die Gemeindeordnung; ein eigenes Finanzhaushalt-/Beschaffungsreglement ist nicht verlinkt</t>
         </is>
       </c>
     </row>
@@ -21917,8 +21766,7 @@
       </c>
       <c r="F83" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-14.12.2012</t>
+          <t>14.12.2012</t>
         </is>
       </c>
       <c r="G83" s="23" t="inlineStr">
@@ -21958,7 +21806,7 @@
       </c>
       <c r="N83" s="42" t="inlineStr">
         <is>
-          <t>manuell geprüft · OK</t>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O83" s="23" t="inlineStr">
@@ -21966,11 +21814,7 @@
           <t>Katalog · hoch</t>
         </is>
       </c>
-      <c r="P83" s="23" t="inlineStr">
-        <is>
-          <t>Manuell geprüft 14.10.2026: OK, Stand ergänzt</t>
-        </is>
-      </c>
+      <c r="P83" s="23" t="n"/>
     </row>
     <row r="84" outlineLevel="1" ht="22.35" customHeight="1">
       <c r="A84" s="23" t="inlineStr">
@@ -22040,7 +21884,7 @@
       </c>
       <c r="N84" s="42" t="inlineStr">
         <is>
-          <t>Kataster · geprüft · OK</t>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O84" s="23" t="inlineStr">
@@ -22116,9 +21960,9 @@
           <t>https://cms.e-mitwirkung.ch/media/wil/Reglement_221013.pdf</t>
         </is>
       </c>
-      <c r="N85" s="46" t="inlineStr">
-        <is>
-          <t>geprüft · Hinweis</t>
+      <c r="N85" s="42" t="inlineStr">
+        <is>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O85" s="23" t="inlineStr">
@@ -22128,7 +21972,7 @@
       </c>
       <c r="P85" s="23" t="inlineStr">
         <is>
-          <t>Manuell geprüft 14.10.2026: Reglement zur Schutzverordnung enthält auch kantonale Schutzobjekte; Zuständigkeit liegt allein bei der Gde Wil. | Hinweis Linkprüfung: PDF ist der Entwurf zur öffentlichen Auflage (13.10.2022), nicht die erlassene Fassung</t>
+          <t>Reglement enthält auch kantonale Schutzobjekte; Zuständigkeit liegt allein bei der Gde Wil. Verlinkt ist der Entwurf zur öffentlichen Auflage (13.10.2022); die erlassene Fassung ist online nicht auffindbar</t>
         </is>
       </c>
     </row>
@@ -22200,7 +22044,7 @@
       </c>
       <c r="N86" s="42" t="inlineStr">
         <is>
-          <t>Kataster · geprüft · OK</t>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O86" s="23" t="inlineStr">
@@ -22210,7 +22054,7 @@
       </c>
       <c r="P86" s="23" t="inlineStr">
         <is>
-          <t>Link identisch mit Baureglement → Inhalt verifizieren | Referenz SRS 7.1-1 ist das Baureglement; eine eigene Energieplanung ist in der Rechtssammlung Wil nicht vorhanden</t>
+          <t>Keine eigene Energieplanung in der Rechtssammlung Wil; Energievorgaben im Baureglement (SRS 7.1-1)</t>
         </is>
       </c>
     </row>
@@ -22235,12 +22079,12 @@
           <t>Abwasserreglement</t>
         </is>
       </c>
-      <c r="E87" s="45" t="inlineStr">
+      <c r="E87" s="23" t="inlineStr">
         <is>
           <t>SRS 7.4.3-6</t>
         </is>
       </c>
-      <c r="F87" s="54" t="n">
+      <c r="F87" s="58" t="n">
         <v>43374</v>
       </c>
       <c r="G87" s="23" t="inlineStr">
@@ -22273,14 +22117,14 @@
           <t>Entwässerungs- und Retentionsanforderungen</t>
         </is>
       </c>
-      <c r="M87" s="43" t="inlineStr">
+      <c r="M87" s="56" t="inlineStr">
         <is>
           <t>https://wil-sg.tlex.ch/app/de/texts_of_law/7.4.3-6</t>
         </is>
       </c>
       <c r="N87" s="42" t="inlineStr">
         <is>
-          <t>manuell geprüft · OK</t>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O87" s="23" t="inlineStr">
@@ -22288,11 +22132,7 @@
           <t>Katalog · hoch</t>
         </is>
       </c>
-      <c r="P87" s="23" t="inlineStr">
-        <is>
-          <t>Manuell geprüft 14.10.2026: OK, Stand ergänzt (geltende Fassung SRS 7.4.3-6)</t>
-        </is>
-      </c>
+      <c r="P87" s="23" t="n"/>
     </row>
     <row r="88" outlineLevel="1" ht="22.35" customHeight="1">
       <c r="A88" s="23" t="inlineStr">
@@ -22362,7 +22202,7 @@
       </c>
       <c r="N88" s="42" t="inlineStr">
         <is>
-          <t>Kataster · geprüft · OK</t>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O88" s="23" t="inlineStr">
@@ -22422,7 +22262,7 @@
       </c>
       <c r="F90" s="23" t="inlineStr">
         <is>
-          <t>01.01.2015</t>
+          <t>18.02.2025</t>
         </is>
       </c>
       <c r="G90" s="23" t="inlineStr">
@@ -22462,7 +22302,7 @@
       </c>
       <c r="N90" s="42" t="inlineStr">
         <is>
-          <t>Kataster · geprüft · OK</t>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O90" s="23" t="inlineStr">
@@ -22472,7 +22312,7 @@
       </c>
       <c r="P90" s="23" t="inlineStr">
         <is>
-          <t>Revisionsstand prüfen (Zonenplan 2026 jünger als BZO 2015)</t>
+          <t>BZO vom 01.01.2015, Revision 18.02.2025</t>
         </is>
       </c>
     </row>
@@ -22542,9 +22382,9 @@
           <t>https://geo.ur.ch/</t>
         </is>
       </c>
-      <c r="N91" s="24" t="inlineStr">
-        <is>
-          <t>Kataster · geprüft · nur Einstiegsseite</t>
+      <c r="N91" s="42" t="inlineStr">
+        <is>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O91" s="23" t="inlineStr">
@@ -22554,7 +22394,7 @@
       </c>
       <c r="P91" s="23" t="inlineStr">
         <is>
-          <t>Katalog-Link = geo.ur.ch (Kartenviewer mit Layern)</t>
+          <t>Kartenviewer geo.ur.ch (Nutzungsplanung)</t>
         </is>
       </c>
     </row>
@@ -22626,7 +22466,7 @@
       </c>
       <c r="N92" s="42" t="inlineStr">
         <is>
-          <t>Kataster · geprüft · OK</t>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O92" s="23" t="inlineStr">
@@ -22704,7 +22544,7 @@
       </c>
       <c r="N93" s="42" t="inlineStr">
         <is>
-          <t>Kataster · geprüft · OK</t>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O93" s="23" t="inlineStr">
@@ -22714,7 +22554,7 @@
       </c>
       <c r="P93" s="23" t="inlineStr">
         <is>
-          <t>Inhaltlich Wasserversorgung, nicht Entwässerung/Retention → Abwasserreglement/GEP fehlt</t>
+          <t>Inhaltlich Wasserversorgung, nicht Entwässerung/Retention → Abwasserreglement/GEP Seelisberg fehlt</t>
         </is>
       </c>
     </row>
@@ -22786,7 +22626,7 @@
       </c>
       <c r="N94" s="42" t="inlineStr">
         <is>
-          <t>manuell geprüft · OK</t>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O94" s="23" t="inlineStr">
@@ -22796,7 +22636,7 @@
       </c>
       <c r="P94" s="23" t="inlineStr">
         <is>
-          <t>Manuell geprüft 14.10.2026: OK (BZO vom 01.01.2015, rev. 18.02.2025)</t>
+          <t>Mehrfach gelistet, weil das Dokument mehrere Q-Dimensionen abdeckt (Q1, Q5); BZO vom 01.01.2015, Revision 18.02.2025</t>
         </is>
       </c>
     </row>
@@ -22851,9 +22691,9 @@
           <t>n. a.</t>
         </is>
       </c>
-      <c r="K95" s="30" t="inlineStr">
-        <is>
-          <t>nicht belegt (Recherche offen)</t>
+      <c r="K95" s="57" t="inlineStr">
+        <is>
+          <t>belegt</t>
         </is>
       </c>
       <c r="L95" s="23" t="inlineStr">
@@ -22868,17 +22708,17 @@
       </c>
       <c r="N95" s="42" t="inlineStr">
         <is>
-          <t>manuell geprüft · OK</t>
+          <t>geprüft · OK</t>
         </is>
       </c>
       <c r="O95" s="23" t="inlineStr">
         <is>
-          <t>Ergänzung · tief</t>
+          <t>Ergänzung · hoch</t>
         </is>
       </c>
       <c r="P95" s="23" t="inlineStr">
         <is>
-          <t>Manuell geprüft 14.10.2026: Link auf Gemeindeordnung ergänzt, OK</t>
+          <t>Verlinkt ist die Gemeindeordnung; ein eigenes Finanzhaushalt-/Beschaffungsreglement ist nicht verlinkt</t>
         </is>
       </c>
     </row>
@@ -25205,7 +25045,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="31.5" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
         <is>
@@ -30865,7 +30704,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="31.5" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
         <is>
